--- a/docs/data/jp/xlsx/4412.xlsx
+++ b/docs/data/jp/xlsx/4412.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -705,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC190"/>
+  <dimension ref="A1:AC216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4745,11 +4748,11 @@
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B53" s="27" t="n">
-        <v>1318</v>
+        <v>1279</v>
       </c>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="29" t="n"/>
@@ -5986,7 +5989,7 @@
     <row r="80">
       <c r="A80" s="41" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C80" s="39" t="n"/>
@@ -6238,400 +6241,578 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G85" s="15">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="15">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="15">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="15">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="15">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="15">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="15">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="15">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="15">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="15">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="15">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="15">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="15">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C85" s="20" t="n">
+      <c r="C86" s="20" t="n">
         <v>167.321</v>
       </c>
-      <c r="D85" s="20" t="n">
+      <c r="D86" s="20" t="n">
         <v>101.381</v>
       </c>
-      <c r="E85" s="20" t="n">
+      <c r="E86" s="20" t="n">
         <v>123.822</v>
       </c>
-      <c r="F85" s="20" t="n">
+      <c r="F86" s="20" t="n">
         <v>114.182</v>
       </c>
-      <c r="G85" s="20" t="n">
+      <c r="G86" s="20" t="n">
         <v>131.335</v>
       </c>
-      <c r="H85" s="20" t="n">
+      <c r="H86" s="20" t="n">
         <v>152.764</v>
       </c>
-      <c r="I85" s="20" t="n">
+      <c r="I86" s="20" t="n">
         <v>159.303</v>
       </c>
-      <c r="J85" s="20" t="n">
+      <c r="J86" s="20" t="n">
         <v>201.223</v>
       </c>
-      <c r="K85" s="20" t="n">
+      <c r="K86" s="20" t="n">
         <v>193.579</v>
       </c>
-      <c r="L85" s="20" t="n">
+      <c r="L86" s="20" t="n">
         <v>190.86</v>
       </c>
-      <c r="M85" s="20" t="n">
+      <c r="M86" s="20" t="n">
         <v>201.135</v>
       </c>
-      <c r="N85" s="20" t="n">
+      <c r="N86" s="20" t="n">
         <v>199.226</v>
       </c>
-      <c r="T85" s="20" t="n">
+      <c r="T86" s="20" t="n">
         <v>78.556</v>
       </c>
-      <c r="U85" s="20" t="n">
+      <c r="U86" s="20" t="n">
         <v>90.54600000000001</v>
       </c>
-      <c r="V85" s="20" t="n">
+      <c r="V86" s="20" t="n">
         <v>114.182</v>
       </c>
-      <c r="W85" s="20" t="n">
+      <c r="W86" s="20" t="n">
         <v>201.223</v>
       </c>
-      <c r="X85" s="20" t="n">
+      <c r="X86" s="20" t="n">
         <v>199.226</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C86" s="12" t="n">
+      <c r="C87" s="12" t="n">
         <v>137.122</v>
       </c>
-      <c r="D86" s="12" t="n">
+      <c r="D87" s="12" t="n">
         <v>153.882</v>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="E87" s="12" t="n">
         <v>195.357</v>
       </c>
-      <c r="F86" s="12" t="n">
+      <c r="F87" s="12" t="n">
         <v>191.707</v>
       </c>
-      <c r="G86" s="12" t="n">
+      <c r="G87" s="12" t="n">
         <v>209.643</v>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>235.411</v>
       </c>
-      <c r="I86" s="12" t="n">
+      <c r="I87" s="12" t="n">
         <v>271.661</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="J87" s="12" t="n">
         <v>293.28</v>
       </c>
-      <c r="K86" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>321.554</v>
       </c>
-      <c r="L86" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>322.006</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>335.637</v>
       </c>
-      <c r="N86" s="12" t="n">
+      <c r="N87" s="12" t="n">
         <v>370.22</v>
       </c>
-      <c r="T86" s="12" t="n">
+      <c r="T87" s="12" t="n">
         <v>128.441</v>
       </c>
-      <c r="U86" s="12" t="n">
+      <c r="U87" s="12" t="n">
         <v>128.404</v>
       </c>
-      <c r="V86" s="12" t="n">
+      <c r="V87" s="12" t="n">
         <v>191.707</v>
       </c>
-      <c r="W86" s="12" t="n">
+      <c r="W87" s="12" t="n">
         <v>293.28</v>
       </c>
-      <c r="X86" s="12" t="n">
+      <c r="X87" s="12" t="n">
         <v>370.22</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>157.64</v>
-      </c>
-      <c r="D87" s="20" t="n">
-        <v>148.802</v>
-      </c>
-      <c r="E87" s="20" t="n">
-        <v>215.503</v>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>187.399</v>
-      </c>
-      <c r="G87" s="20" t="n">
-        <v>201.036</v>
-      </c>
-      <c r="H87" s="20" t="n">
-        <v>211.547</v>
-      </c>
-      <c r="I87" s="20" t="n">
-        <v>246.862</v>
-      </c>
-      <c r="J87" s="20" t="n">
-        <v>243.294</v>
-      </c>
-      <c r="K87" s="20" t="n">
-        <v>264.995</v>
-      </c>
-      <c r="L87" s="20" t="n">
-        <v>273.641</v>
-      </c>
-      <c r="M87" s="20" t="n">
-        <v>291.327</v>
-      </c>
-      <c r="N87" s="20" t="n">
-        <v>257.451</v>
-      </c>
-      <c r="T87" s="20" t="n">
-        <v>121.925</v>
-      </c>
-      <c r="U87" s="20" t="n">
-        <v>164.069</v>
-      </c>
-      <c r="V87" s="20" t="n">
-        <v>187.399</v>
-      </c>
-      <c r="W87" s="20" t="n">
-        <v>243.294</v>
-      </c>
-      <c r="X87" s="20" t="n">
-        <v>257.451</v>
-      </c>
-    </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="n">
-        <v>-20.517</v>
-      </c>
-      <c r="D88" s="12" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="E88" s="12" t="n">
-        <v>-20.146</v>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>4.308</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>8.606</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>23.864</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>24.799</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>49.987</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>56.558</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>48.366</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>44.309</v>
-      </c>
-      <c r="N88" s="12" t="n">
-        <v>112.769</v>
-      </c>
-      <c r="T88" s="12" t="n">
-        <v>6.516</v>
-      </c>
-      <c r="U88" s="12" t="n">
-        <v>-35.666</v>
-      </c>
-      <c r="V88" s="12" t="n">
-        <v>4.308</v>
-      </c>
-      <c r="W88" s="12" t="n">
-        <v>49.987</v>
-      </c>
-      <c r="X88" s="12" t="n">
-        <v>112.769</v>
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G88" s="15">
+        <f>IF(OR(G87="",C87=""),"",IF(C87&lt;=0,"",IFERROR(G87/C87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="15">
+        <f>IF(OR(H87="",D87=""),"",IF(D87&lt;=0,"",IFERROR(H87/D87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="15">
+        <f>IF(OR(I87="",E87=""),"",IF(E87&lt;=0,"",IFERROR(I87/E87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="15">
+        <f>IF(OR(J87="",F87=""),"",IF(F87&lt;=0,"",IFERROR(J87/F87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="15">
+        <f>IF(OR(K87="",G87=""),"",IF(G87&lt;=0,"",IFERROR(K87/G87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="15">
+        <f>IF(OR(L87="",H87=""),"",IF(H87&lt;=0,"",IFERROR(L87/H87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="15">
+        <f>IF(OR(M87="",I87=""),"",IF(I87&lt;=0,"",IFERROR(M87/I87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="15">
+        <f>IF(OR(N87="",J87=""),"",IF(J87&lt;=0,"",IFERROR(N87/J87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T88" s="15">
+        <f>IF(OR(T87="",S87=""),"",IF(S87&lt;=0,"",IFERROR(T87/S87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U88" s="15">
+        <f>IF(OR(U87="",T87=""),"",IF(T87&lt;=0,"",IFERROR(U87/T87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="15">
+        <f>IF(OR(V87="",U87=""),"",IF(U87&lt;=0,"",IFERROR(V87/U87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="15">
+        <f>IF(OR(W87="",V87=""),"",IF(V87&lt;=0,"",IFERROR(W87/V87-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="15">
+        <f>IF(OR(X87="",W87=""),"",IF(W87&lt;=0,"",IFERROR(X87/W87-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="18" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C89" s="20" t="n">
-        <v>0</v>
+        <v>157.64</v>
       </c>
       <c r="D89" s="20" t="n">
-        <v>0.003</v>
+        <v>148.802</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.003</v>
+        <v>215.503</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>0.044</v>
+        <v>187.399</v>
       </c>
       <c r="G89" s="20" t="n">
-        <v>0.016</v>
+        <v>201.036</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>0.497</v>
+        <v>211.547</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>0.036</v>
+        <v>246.862</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>1.393</v>
+        <v>243.294</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>0.047</v>
+        <v>264.995</v>
       </c>
       <c r="L89" s="20" t="n">
-        <v>1.659</v>
+        <v>273.641</v>
       </c>
       <c r="M89" s="20" t="n">
-        <v>0.065</v>
+        <v>291.327</v>
       </c>
       <c r="N89" s="20" t="n">
-        <v>1.838</v>
+        <v>257.451</v>
       </c>
       <c r="T89" s="20" t="n">
-        <v>0.003</v>
+        <v>121.925</v>
       </c>
       <c r="U89" s="20" t="n">
-        <v>0.003</v>
+        <v>164.069</v>
       </c>
       <c r="V89" s="20" t="n">
-        <v>0.044</v>
+        <v>187.399</v>
       </c>
       <c r="W89" s="20" t="n">
-        <v>1.393</v>
+        <v>243.294</v>
       </c>
       <c r="X89" s="20" t="n">
-        <v>1.838</v>
+        <v>257.451</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="20" t="n">
-        <v>0</v>
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>-20.517</v>
+      </c>
+      <c r="D90" s="12" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>-20.146</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>4.308</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>8.606</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>23.864</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>24.799</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>49.987</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>56.558</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>48.366</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>44.309</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>112.769</v>
+      </c>
+      <c r="T90" s="12" t="n">
+        <v>6.516</v>
+      </c>
+      <c r="U90" s="12" t="n">
+        <v>-35.666</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>4.308</v>
+      </c>
+      <c r="W90" s="12" t="n">
+        <v>49.987</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>112.769</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
-        <is>
-          <t>포상금 수익</t>
-        </is>
-      </c>
-      <c r="E91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="20" t="n">
-        <v>0</v>
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C91" s="15">
+        <f>IF(OR(C90="",C84=""),"",IF(C84&lt;=0,"",IFERROR(C90/C84,"")))</f>
+        <v/>
+      </c>
+      <c r="D91" s="15">
+        <f>IF(OR(D90="",D84=""),"",IF(D84&lt;=0,"",IFERROR(D90/D84,"")))</f>
+        <v/>
+      </c>
+      <c r="E91" s="15">
+        <f>IF(OR(E90="",E84=""),"",IF(E84&lt;=0,"",IFERROR(E90/E84,"")))</f>
+        <v/>
+      </c>
+      <c r="F91" s="15">
+        <f>IF(OR(F90="",F84=""),"",IF(F84&lt;=0,"",IFERROR(F90/F84,"")))</f>
+        <v/>
+      </c>
+      <c r="G91" s="15">
+        <f>IF(OR(G90="",G84=""),"",IF(G84&lt;=0,"",IFERROR(G90/G84,"")))</f>
+        <v/>
+      </c>
+      <c r="H91" s="15">
+        <f>IF(OR(H90="",H84=""),"",IF(H84&lt;=0,"",IFERROR(H90/H84,"")))</f>
+        <v/>
+      </c>
+      <c r="I91" s="15">
+        <f>IF(OR(I90="",I84=""),"",IF(I84&lt;=0,"",IFERROR(I90/I84,"")))</f>
+        <v/>
+      </c>
+      <c r="J91" s="15">
+        <f>IF(OR(J90="",J84=""),"",IF(J84&lt;=0,"",IFERROR(J90/J84,"")))</f>
+        <v/>
+      </c>
+      <c r="K91" s="15">
+        <f>IF(OR(K90="",K84=""),"",IF(K84&lt;=0,"",IFERROR(K90/K84,"")))</f>
+        <v/>
+      </c>
+      <c r="L91" s="15">
+        <f>IF(OR(L90="",L84=""),"",IF(L84&lt;=0,"",IFERROR(L90/L84,"")))</f>
+        <v/>
+      </c>
+      <c r="M91" s="15">
+        <f>IF(OR(M90="",M84=""),"",IF(M84&lt;=0,"",IFERROR(M90/M84,"")))</f>
+        <v/>
+      </c>
+      <c r="N91" s="15">
+        <f>IF(OR(N90="",N84=""),"",IF(N84&lt;=0,"",IFERROR(N90/N84,"")))</f>
+        <v/>
+      </c>
+      <c r="T91" s="15">
+        <f>IF(OR(T90="",T84=""),"",IF(T84&lt;=0,"",IFERROR(T90/T84,"")))</f>
+        <v/>
+      </c>
+      <c r="U91" s="15">
+        <f>IF(OR(U90="",U84=""),"",IF(U84&lt;=0,"",IFERROR(U90/U84,"")))</f>
+        <v/>
+      </c>
+      <c r="V91" s="15">
+        <f>IF(OR(V90="",V84=""),"",IF(V84&lt;=0,"",IFERROR(V90/V84,"")))</f>
+        <v/>
+      </c>
+      <c r="W91" s="15">
+        <f>IF(OR(W90="",W84=""),"",IF(W84&lt;=0,"",IFERROR(W90/W84,"")))</f>
+        <v/>
+      </c>
+      <c r="X91" s="15">
+        <f>IF(OR(X90="",X84=""),"",IF(X84&lt;=0,"",IFERROR(X90/X84,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>업무수탁료</t>
-        </is>
-      </c>
-      <c r="T92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="20" t="n">
-        <v>0</v>
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G92" s="15">
+        <f>IF(OR(G90="",C90=""),"",IF(C90&lt;=0,"",IFERROR(G90/C90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H92" s="15">
+        <f>IF(OR(H90="",D90=""),"",IF(D90&lt;=0,"",IFERROR(H90/D90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I92" s="15">
+        <f>IF(OR(I90="",E90=""),"",IF(E90&lt;=0,"",IFERROR(I90/E90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J92" s="15">
+        <f>IF(OR(J90="",F90=""),"",IF(F90&lt;=0,"",IFERROR(J90/F90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K92" s="15">
+        <f>IF(OR(K90="",G90=""),"",IF(G90&lt;=0,"",IFERROR(K90/G90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L92" s="15">
+        <f>IF(OR(L90="",H90=""),"",IF(H90&lt;=0,"",IFERROR(L90/H90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M92" s="15">
+        <f>IF(OR(M90="",I90=""),"",IF(I90&lt;=0,"",IFERROR(M90/I90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="15">
+        <f>IF(OR(N90="",J90=""),"",IF(J90&lt;=0,"",IFERROR(N90/J90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T92" s="15">
+        <f>IF(OR(T90="",S90=""),"",IF(S90&lt;=0,"",IFERROR(T90/S90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U92" s="15">
+        <f>IF(OR(U90="",T90=""),"",IF(T90&lt;=0,"",IFERROR(U90/T90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V92" s="15">
+        <f>IF(OR(V90="",U90=""),"",IF(U90&lt;=0,"",IFERROR(V90/U90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W92" s="15">
+        <f>IF(OR(W90="",V90=""),"",IF(V90&lt;=0,"",IFERROR(W90/V90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X92" s="15">
+        <f>IF(OR(X90="",W90=""),"",IF(W90&lt;=0,"",IFERROR(X90/W90-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>유가증권 이자</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E93" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="G93" s="20" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <v>0.036</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>0</v>
+        <v>1.393</v>
+      </c>
+      <c r="K93" s="20" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="L93" s="20" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="M93" s="20" t="n">
+        <v>0.065</v>
       </c>
       <c r="N93" s="20" t="n">
-        <v>1.103</v>
+        <v>1.838</v>
+      </c>
+      <c r="T93" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="U93" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V93" s="20" t="n">
+        <v>0.044</v>
       </c>
       <c r="W93" s="20" t="n">
-        <v>0</v>
+        <v>1.393</v>
       </c>
       <c r="X93" s="20" t="n">
-        <v>1.103</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D94" s="20" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E94" s="20" t="n">
         <v>0</v>
@@ -6640,30 +6821,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N94" s="20" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="T94" s="20" t="n">
         <v>0</v>
       </c>
       <c r="U94" s="20" t="n">
@@ -6673,194 +6839,74 @@
         <v>0</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="X94" s="20" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C95" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D95" s="20" t="n">
-        <v>0.008999999999999999</v>
+          <t>포상금 수익</t>
+        </is>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="G95" s="20" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H95" s="20" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="I95" s="20" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J95" s="20" t="n">
-        <v>1.398</v>
-      </c>
-      <c r="K95" s="20" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="L95" s="20" t="n">
-        <v>1.659</v>
-      </c>
-      <c r="M95" s="20" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="N95" s="20" t="n">
-        <v>3.019</v>
+        <v>0</v>
       </c>
       <c r="T95" s="20" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U95" s="20" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="V95" s="20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="W95" s="20" t="n">
-        <v>1.398</v>
-      </c>
-      <c r="X95" s="20" t="n">
-        <v>3.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="D96" s="20" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E96" s="20" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G96" s="20" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="H96" s="20" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="I96" s="20" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="J96" s="20" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K96" s="20" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="L96" s="20" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="M96" s="20" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="N96" s="20" t="n">
-        <v>0.311</v>
+          <t>업무수탁료</t>
+        </is>
+      </c>
+      <c r="T96" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="U96" s="20" t="n">
         <v>0</v>
-      </c>
-      <c r="V96" s="20" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="W96" s="20" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="X96" s="20" t="n">
-        <v>0.311</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
-      </c>
-      <c r="C97" s="20" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="D97" s="20" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="E97" s="20" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="F97" s="20" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="G97" s="20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H97" s="20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I97" s="20" t="n">
-        <v>0.07000000000000001</v>
+          <t>유가증권 이자</t>
+        </is>
       </c>
       <c r="J97" s="20" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="K97" s="20" t="n">
-        <v>1.355</v>
-      </c>
-      <c r="L97" s="20" t="n">
-        <v>1.169</v>
-      </c>
-      <c r="M97" s="20" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="N97" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="T97" s="20" t="n">
-        <v>-0.127</v>
-      </c>
-      <c r="U97" s="20" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="V97" s="20" t="n">
-        <v>0.066</v>
+        <v>1.103</v>
       </c>
       <c r="W97" s="20" t="n">
-        <v>-0.082</v>
+        <v>0</v>
       </c>
       <c r="X97" s="20" t="n">
-        <v>0.05</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D98" s="20" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E98" s="20" t="n">
         <v>0</v>
@@ -6869,16 +6915,16 @@
         <v>0</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>14.011</v>
+        <v>0.002</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="K98" s="20" t="n">
         <v>0</v>
@@ -6887,10 +6933,10 @@
         <v>0</v>
       </c>
       <c r="M98" s="20" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N98" s="20" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="T98" s="20" t="n">
         <v>0</v>
@@ -6902,191 +6948,194 @@
         <v>0</v>
       </c>
       <c r="W98" s="20" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="X98" s="20" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C99" s="20" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D99" s="20" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>0.002</v>
+        <v>0.045</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>0.075</v>
+        <v>0.591</v>
       </c>
       <c r="I99" s="20" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="J99" s="20" t="n">
+        <v>1.398</v>
+      </c>
+      <c r="K99" s="20" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="L99" s="20" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="M99" s="20" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="N99" s="20" t="n">
+        <v>3.019</v>
+      </c>
+      <c r="T99" s="20" t="n">
         <v>0.003</v>
       </c>
-      <c r="J99" s="20" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="K99" s="20" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="L99" s="20" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="M99" s="20" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="N99" s="20" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="T99" s="20" t="n">
-        <v>-0.003</v>
-      </c>
       <c r="U99" s="20" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="V99" s="20" t="n">
-        <v>0.002</v>
+        <v>0.045</v>
       </c>
       <c r="W99" s="20" t="n">
-        <v>0.113</v>
+        <v>1.398</v>
       </c>
       <c r="X99" s="20" t="n">
-        <v>0.143</v>
+        <v>3.019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
-        <v>0.475</v>
+        <v>0.355</v>
       </c>
       <c r="D100" s="20" t="n">
-        <v>1.126</v>
+        <v>0.43</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>0.741</v>
+        <v>0.424</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>0.479</v>
+        <v>0.41</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>14.821</v>
+        <v>0.406</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>0.819</v>
+        <v>0.394</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>0.556</v>
+        <v>0.484</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>0.414</v>
+        <v>0.383</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1.742</v>
+        <v>0.349</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>1.597</v>
+        <v>0.331</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>0.517</v>
+        <v>0.334</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="T100" s="20" t="n">
-        <v>-0.13</v>
+        <v>0.311</v>
       </c>
       <c r="U100" s="20" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="V100" s="20" t="n">
-        <v>0.479</v>
+        <v>0.41</v>
       </c>
       <c r="W100" s="20" t="n">
-        <v>0.414</v>
+        <v>0.383</v>
       </c>
       <c r="X100" s="20" t="n">
-        <v>0.505</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>-20.953</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>3.965</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>-20.886</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>3.874</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>-6.195</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>23.634</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>24.289</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>50.972</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>54.864</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>48.428</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="N101" s="12" t="n">
-        <v>115.283</v>
-      </c>
-      <c r="T101" s="12" t="n">
-        <v>6.649</v>
-      </c>
-      <c r="U101" s="12" t="n">
-        <v>-35.751</v>
-      </c>
-      <c r="V101" s="12" t="n">
-        <v>3.874</v>
-      </c>
-      <c r="W101" s="12" t="n">
-        <v>50.972</v>
-      </c>
-      <c r="X101" s="12" t="n">
-        <v>115.283</v>
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="D101" s="20" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="E101" s="20" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F101" s="20" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="G101" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H101" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I101" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J101" s="20" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="K101" s="20" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="L101" s="20" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="M101" s="20" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="N101" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T101" s="20" t="n">
+        <v>-0.127</v>
+      </c>
+      <c r="U101" s="20" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="V101" s="20" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="W101" s="20" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="X101" s="20" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
-        </is>
+          <t>주식교부비</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="20" t="n">
         <v>0</v>
@@ -7094,6 +7143,30 @@
       <c r="F102" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="G102" s="20" t="n">
+        <v>14.011</v>
+      </c>
+      <c r="H102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="T102" s="20" t="n">
         <v>0</v>
       </c>
@@ -7101,1339 +7174,1411 @@
         <v>0</v>
       </c>
       <c r="V102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="E103" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="G103" s="20" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H103" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I103" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J103" s="20" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="K103" s="20" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="L103" s="20" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M103" s="20" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="N103" s="20" t="n">
+        <v>0.143</v>
       </c>
       <c r="T103" s="20" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="U103" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="20" t="n">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="W103" s="20" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="X103" s="20" t="n">
+        <v>0.143</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D104" s="20" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="F104" s="20" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="G104" s="20" t="n">
+        <v>14.821</v>
+      </c>
+      <c r="H104" s="20" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="I104" s="20" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="J104" s="20" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="K104" s="20" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="L104" s="20" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="M104" s="20" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="N104" s="20" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="T104" s="20" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="U104" s="20" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="V104" s="20" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="W104" s="20" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="X104" s="20" t="n">
+        <v>0.505</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
         <v>-20.953</v>
       </c>
-      <c r="D104" s="12" t="n">
+      <c r="D105" s="12" t="n">
         <v>3.965</v>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="E105" s="12" t="n">
         <v>-20.886</v>
       </c>
-      <c r="F104" s="12" t="n">
+      <c r="F105" s="12" t="n">
         <v>3.874</v>
       </c>
-      <c r="G104" s="12" t="n">
+      <c r="G105" s="12" t="n">
         <v>-6.195</v>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H105" s="12" t="n">
         <v>23.634</v>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="I105" s="12" t="n">
         <v>24.289</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="J105" s="12" t="n">
         <v>50.972</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="K105" s="12" t="n">
         <v>54.864</v>
       </c>
-      <c r="L104" s="12" t="n">
+      <c r="L105" s="12" t="n">
         <v>48.428</v>
       </c>
-      <c r="M104" s="12" t="n">
+      <c r="M105" s="12" t="n">
         <v>44.2</v>
       </c>
-      <c r="N104" s="12" t="n">
+      <c r="N105" s="12" t="n">
         <v>115.283</v>
       </c>
-      <c r="T104" s="12" t="n">
+      <c r="T105" s="12" t="n">
         <v>6.649</v>
       </c>
-      <c r="U104" s="12" t="n">
+      <c r="U105" s="12" t="n">
         <v>-35.751</v>
       </c>
-      <c r="V104" s="12" t="n">
+      <c r="V105" s="12" t="n">
         <v>3.874</v>
       </c>
-      <c r="W104" s="12" t="n">
+      <c r="W105" s="12" t="n">
         <v>50.972</v>
       </c>
-      <c r="X104" s="12" t="n">
+      <c r="X105" s="12" t="n">
         <v>115.283</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C105" s="20" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="D105" s="20" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="E105" s="20" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="F105" s="20" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="G105" s="20" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="H105" s="20" t="n">
-        <v>4.416</v>
-      </c>
-      <c r="I105" s="20" t="n">
-        <v>5.725</v>
-      </c>
-      <c r="J105" s="20" t="n">
-        <v>10.365</v>
-      </c>
-      <c r="K105" s="20" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="L105" s="20" t="n">
-        <v>7.481</v>
-      </c>
-      <c r="M105" s="20" t="n">
-        <v>9.351000000000001</v>
-      </c>
-      <c r="N105" s="20" t="n">
-        <v>11.968</v>
-      </c>
-      <c r="T105" s="20" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="U105" s="20" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="V105" s="20" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="W105" s="20" t="n">
-        <v>10.365</v>
-      </c>
-      <c r="X105" s="20" t="n">
-        <v>11.968</v>
-      </c>
-    </row>
     <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C106" s="20" t="n">
-        <v>-0.745</v>
-      </c>
-      <c r="D106" s="20" t="n">
-        <v>-0.357</v>
-      </c>
-      <c r="E106" s="20" t="n">
-        <v>-0.327</v>
-      </c>
-      <c r="F106" s="20" t="n">
-        <v>-1.252</v>
-      </c>
-      <c r="G106" s="20" t="n">
-        <v>-1.294</v>
-      </c>
-      <c r="H106" s="20" t="n">
-        <v>-1.202</v>
-      </c>
-      <c r="I106" s="20" t="n">
-        <v>-0.544</v>
-      </c>
-      <c r="J106" s="20" t="n">
-        <v>-37.511</v>
-      </c>
-      <c r="K106" s="20" t="n">
-        <v>-0.597</v>
-      </c>
-      <c r="L106" s="20" t="n">
-        <v>1.528</v>
-      </c>
-      <c r="M106" s="20" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="N106" s="20" t="n">
-        <v>-25.876</v>
-      </c>
-      <c r="T106" s="20" t="n">
-        <v>-0.533</v>
-      </c>
-      <c r="U106" s="20" t="n">
-        <v>9.411</v>
-      </c>
-      <c r="V106" s="20" t="n">
-        <v>-1.252</v>
-      </c>
-      <c r="W106" s="20" t="n">
-        <v>-37.511</v>
-      </c>
-      <c r="X106" s="20" t="n">
-        <v>-25.876</v>
+      <c r="A106" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G106" s="15">
+        <f>IF(OR(G105="",C105=""),"",IF(C105&lt;=0,"",IFERROR(G105/C105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H106" s="15">
+        <f>IF(OR(H105="",D105=""),"",IF(D105&lt;=0,"",IFERROR(H105/D105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I106" s="15">
+        <f>IF(OR(I105="",E105=""),"",IF(E105&lt;=0,"",IFERROR(I105/E105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J106" s="15">
+        <f>IF(OR(J105="",F105=""),"",IF(F105&lt;=0,"",IFERROR(J105/F105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K106" s="15">
+        <f>IF(OR(K105="",G105=""),"",IF(G105&lt;=0,"",IFERROR(K105/G105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L106" s="15">
+        <f>IF(OR(L105="",H105=""),"",IF(H105&lt;=0,"",IFERROR(L105/H105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M106" s="15">
+        <f>IF(OR(M105="",I105=""),"",IF(I105&lt;=0,"",IFERROR(M105/I105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N106" s="15">
+        <f>IF(OR(N105="",J105=""),"",IF(J105&lt;=0,"",IFERROR(N105/J105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T106" s="15">
+        <f>IF(OR(T105="",S105=""),"",IF(S105&lt;=0,"",IFERROR(T105/S105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U106" s="15">
+        <f>IF(OR(U105="",T105=""),"",IF(T105&lt;=0,"",IFERROR(U105/T105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V106" s="15">
+        <f>IF(OR(V105="",U105=""),"",IF(U105&lt;=0,"",IFERROR(V105/U105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W106" s="15">
+        <f>IF(OR(W105="",V105=""),"",IF(V105&lt;=0,"",IFERROR(W105/V105-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X106" s="15">
+        <f>IF(OR(X105="",W105=""),"",IF(W105&lt;=0,"",IFERROR(X105/W105-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C107" s="20" t="n">
-        <v>-0.672</v>
-      </c>
-      <c r="D107" s="20" t="n">
-        <v>-0.285</v>
+          <t>투자유가증권 평가손실</t>
+        </is>
       </c>
       <c r="E107" s="20" t="n">
-        <v>-0.254</v>
+        <v>0</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="G107" s="20" t="n">
-        <v>-0.721</v>
-      </c>
-      <c r="H107" s="20" t="n">
-        <v>3.213</v>
-      </c>
-      <c r="I107" s="20" t="n">
-        <v>5.181</v>
-      </c>
-      <c r="J107" s="20" t="n">
-        <v>-27.145</v>
-      </c>
-      <c r="K107" s="20" t="n">
-        <v>7.207</v>
-      </c>
-      <c r="L107" s="20" t="n">
-        <v>9.010999999999999</v>
-      </c>
-      <c r="M107" s="20" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="N107" s="20" t="n">
-        <v>-13.909</v>
+        <v>0</v>
       </c>
       <c r="T107" s="20" t="n">
-        <v>-0.46</v>
+        <v>0</v>
       </c>
       <c r="U107" s="20" t="n">
-        <v>9.483000000000001</v>
+        <v>0</v>
       </c>
       <c r="V107" s="20" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="W107" s="20" t="n">
-        <v>-27.145</v>
-      </c>
-      <c r="X107" s="20" t="n">
-        <v>-13.909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="n">
-        <v>-20.28</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>-20.631</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>-5.474</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>20.421</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>19.108</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>78.117</v>
-      </c>
-      <c r="K108" s="12" t="n">
-        <v>47.656</v>
-      </c>
-      <c r="L108" s="12" t="n">
-        <v>39.418</v>
-      </c>
-      <c r="M108" s="12" t="n">
-        <v>38.48</v>
-      </c>
-      <c r="N108" s="12" t="n">
-        <v>129.192</v>
-      </c>
-      <c r="T108" s="12" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="U108" s="12" t="n">
-        <v>-45.236</v>
-      </c>
-      <c r="V108" s="12" t="n">
-        <v>4.814</v>
-      </c>
-      <c r="W108" s="12" t="n">
-        <v>78.117</v>
-      </c>
-      <c r="X108" s="12" t="n">
-        <v>129.192</v>
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>-20.953</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>3.965</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>-20.886</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>3.874</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>-6.195</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>23.634</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>24.289</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>50.972</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>54.864</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>48.428</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="N109" s="12" t="n">
+        <v>115.283</v>
+      </c>
+      <c r="T109" s="12" t="n">
+        <v>6.649</v>
+      </c>
+      <c r="U109" s="12" t="n">
+        <v>-35.751</v>
+      </c>
+      <c r="V109" s="12" t="n">
+        <v>3.874</v>
+      </c>
+      <c r="W109" s="12" t="n">
+        <v>50.972</v>
+      </c>
+      <c r="X109" s="12" t="n">
+        <v>115.283</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="16" t="inlineStr">
-        <is>
-          <t>부문 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B110" s="42" t="inlineStr">
-        <is>
-          <t>부문 · 항목</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="16" t="n"/>
-      <c r="G110" s="16" t="n"/>
-      <c r="H110" s="16" t="n"/>
-      <c r="I110" s="16" t="n"/>
-      <c r="J110" s="16" t="n"/>
-      <c r="K110" s="16" t="n"/>
-      <c r="L110" s="16" t="n"/>
-      <c r="M110" s="16" t="n"/>
-      <c r="N110" s="16" t="n"/>
-      <c r="O110" s="16" t="n"/>
-      <c r="P110" s="16" t="n"/>
-      <c r="Q110" s="16" t="n"/>
-      <c r="R110" s="16" t="n"/>
-      <c r="S110" s="16" t="n"/>
-      <c r="T110" s="16" t="n"/>
-      <c r="U110" s="16" t="n"/>
-      <c r="V110" s="16" t="n"/>
-      <c r="W110" s="16" t="n"/>
-      <c r="X110" s="16" t="n"/>
-      <c r="Y110" s="16" t="n"/>
-      <c r="Z110" s="16" t="n"/>
-      <c r="AA110" s="16" t="n"/>
-      <c r="AB110" s="16" t="n"/>
-      <c r="AC110" s="16" t="n"/>
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D110" s="20" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="G110" s="20" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="H110" s="20" t="n">
+        <v>4.416</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>5.725</v>
+      </c>
+      <c r="J110" s="20" t="n">
+        <v>10.365</v>
+      </c>
+      <c r="K110" s="20" t="n">
+        <v>7.805</v>
+      </c>
+      <c r="L110" s="20" t="n">
+        <v>7.481</v>
+      </c>
+      <c r="M110" s="20" t="n">
+        <v>9.351000000000001</v>
+      </c>
+      <c r="N110" s="20" t="n">
+        <v>11.968</v>
+      </c>
+      <c r="T110" s="20" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="U110" s="20" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="V110" s="20" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="W110" s="20" t="n">
+        <v>10.365</v>
+      </c>
+      <c r="X110" s="20" t="n">
+        <v>11.968</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>2024.1Q</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="M111" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="O111" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P111" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q111" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R111" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S111" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T111" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U111" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V111" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W111" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X111" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y111" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z111" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA111" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB111" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC111" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="n">
+        <v>-0.745</v>
+      </c>
+      <c r="D111" s="20" t="n">
+        <v>-0.357</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>-0.327</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>-1.252</v>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>-1.294</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>-1.202</v>
+      </c>
+      <c r="I111" s="20" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="J111" s="20" t="n">
+        <v>-37.511</v>
+      </c>
+      <c r="K111" s="20" t="n">
+        <v>-0.597</v>
+      </c>
+      <c r="L111" s="20" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="M111" s="20" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="N111" s="20" t="n">
+        <v>-25.876</v>
+      </c>
+      <c r="T111" s="20" t="n">
+        <v>-0.533</v>
+      </c>
+      <c r="U111" s="20" t="n">
+        <v>9.411</v>
+      </c>
+      <c r="V111" s="20" t="n">
+        <v>-1.252</v>
+      </c>
+      <c r="W111" s="20" t="n">
+        <v>-37.511</v>
+      </c>
+      <c r="X111" s="20" t="n">
+        <v>-25.876</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="D112" s="20" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="E112" s="20" t="n">
+        <v>-0.254</v>
+      </c>
+      <c r="F112" s="20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="G112" s="20" t="n">
+        <v>-0.721</v>
+      </c>
+      <c r="H112" s="20" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="I112" s="20" t="n">
+        <v>5.181</v>
+      </c>
+      <c r="J112" s="20" t="n">
+        <v>-27.145</v>
+      </c>
+      <c r="K112" s="20" t="n">
+        <v>7.207</v>
+      </c>
+      <c r="L112" s="20" t="n">
+        <v>9.010999999999999</v>
+      </c>
+      <c r="M112" s="20" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="N112" s="20" t="n">
+        <v>-13.909</v>
+      </c>
+      <c r="T112" s="20" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="U112" s="20" t="n">
+        <v>9.483000000000001</v>
+      </c>
+      <c r="V112" s="20" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="W112" s="20" t="n">
+        <v>-27.145</v>
+      </c>
+      <c r="X112" s="20" t="n">
+        <v>-13.909</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>-20.28</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>4.249</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>-20.631</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>-5.474</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>20.421</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <v>19.108</v>
+      </c>
+      <c r="J113" s="12" t="n">
+        <v>78.117</v>
+      </c>
+      <c r="K113" s="12" t="n">
+        <v>47.656</v>
+      </c>
+      <c r="L113" s="12" t="n">
+        <v>39.418</v>
+      </c>
+      <c r="M113" s="12" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="N113" s="12" t="n">
+        <v>129.192</v>
+      </c>
+      <c r="T113" s="12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="U113" s="12" t="n">
+        <v>-45.236</v>
+      </c>
+      <c r="V113" s="12" t="n">
+        <v>4.814</v>
+      </c>
+      <c r="W113" s="12" t="n">
+        <v>78.117</v>
+      </c>
+      <c r="X113" s="12" t="n">
+        <v>129.192</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G114" s="15">
+        <f>IF(OR(G113="",C113=""),"",IF(C113&lt;=0,"",IFERROR(G113/C113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H114" s="15">
+        <f>IF(OR(H113="",D113=""),"",IF(D113&lt;=0,"",IFERROR(H113/D113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I114" s="15">
+        <f>IF(OR(I113="",E113=""),"",IF(E113&lt;=0,"",IFERROR(I113/E113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J114" s="15">
+        <f>IF(OR(J113="",F113=""),"",IF(F113&lt;=0,"",IFERROR(J113/F113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K114" s="15">
+        <f>IF(OR(K113="",G113=""),"",IF(G113&lt;=0,"",IFERROR(K113/G113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L114" s="15">
+        <f>IF(OR(L113="",H113=""),"",IF(H113&lt;=0,"",IFERROR(L113/H113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M114" s="15">
+        <f>IF(OR(M113="",I113=""),"",IF(I113&lt;=0,"",IFERROR(M113/I113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N114" s="15">
+        <f>IF(OR(N113="",J113=""),"",IF(J113&lt;=0,"",IFERROR(N113/J113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T114" s="15">
+        <f>IF(OR(T113="",S113=""),"",IF(S113&lt;=0,"",IFERROR(T113/S113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U114" s="15">
+        <f>IF(OR(U113="",T113=""),"",IF(T113&lt;=0,"",IFERROR(U113/T113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V114" s="15">
+        <f>IF(OR(V113="",U113=""),"",IF(U113&lt;=0,"",IFERROR(V113/U113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W114" s="15">
+        <f>IF(OR(W113="",V113=""),"",IF(V113&lt;=0,"",IFERROR(W113/V113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X114" s="15">
+        <f>IF(OR(X113="",W113=""),"",IF(W113&lt;=0,"",IFERROR(X113/W113-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="16" t="inlineStr">
+        <is>
+          <t>부문 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B116" s="42" t="inlineStr">
+        <is>
+          <t>부문 · 항목</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="n"/>
+      <c r="D116" s="16" t="n"/>
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="n"/>
+      <c r="G116" s="16" t="n"/>
+      <c r="H116" s="16" t="n"/>
+      <c r="I116" s="16" t="n"/>
+      <c r="J116" s="16" t="n"/>
+      <c r="K116" s="16" t="n"/>
+      <c r="L116" s="16" t="n"/>
+      <c r="M116" s="16" t="n"/>
+      <c r="N116" s="16" t="n"/>
+      <c r="O116" s="16" t="n"/>
+      <c r="P116" s="16" t="n"/>
+      <c r="Q116" s="16" t="n"/>
+      <c r="R116" s="16" t="n"/>
+      <c r="S116" s="16" t="n"/>
+      <c r="T116" s="16" t="n"/>
+      <c r="U116" s="16" t="n"/>
+      <c r="V116" s="16" t="n"/>
+      <c r="W116" s="16" t="n"/>
+      <c r="X116" s="16" t="n"/>
+      <c r="Y116" s="16" t="n"/>
+      <c r="Z116" s="16" t="n"/>
+      <c r="AA116" s="16" t="n"/>
+      <c r="AB116" s="16" t="n"/>
+      <c r="AC116" s="16" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>2024.1Q</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R117" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S117" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T117" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U117" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V117" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X117" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y117" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z117" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA117" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB117" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC117" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
           <t>BuddycomBusinessReportableSegmentMember · 외부 고객 매출</t>
         </is>
       </c>
-      <c r="C112" s="20" t="n">
+      <c r="C118" s="20" t="n">
         <v>303.07</v>
       </c>
-      <c r="D112" s="20" t="n">
+      <c r="D118" s="20" t="n">
         <v>253.889</v>
       </c>
-      <c r="E112" s="20" t="n">
+      <c r="E118" s="20" t="n">
         <v>317.837</v>
       </c>
-      <c r="F112" s="20" t="n">
+      <c r="F118" s="20" t="n">
         <v>304.565</v>
       </c>
-      <c r="G112" s="20" t="n">
+      <c r="G118" s="20" t="n">
         <v>339.653</v>
       </c>
-      <c r="H112" s="20" t="n">
+      <c r="H118" s="20" t="n">
         <v>388.101</v>
       </c>
-      <c r="I112" s="20" t="n">
+      <c r="I118" s="20" t="n">
         <v>430.888</v>
       </c>
-      <c r="J112" s="20" t="n">
+      <c r="J118" s="20" t="n">
         <v>494.428</v>
       </c>
-      <c r="K112" s="20" t="n">
+      <c r="K118" s="20" t="n">
         <v>515.058</v>
       </c>
-      <c r="L112" s="20" t="n">
+      <c r="L118" s="20" t="n">
         <v>512.7910000000001</v>
       </c>
-      <c r="M112" s="20" t="n">
+      <c r="M118" s="20" t="n">
         <v>536.706</v>
       </c>
-      <c r="N112" s="20" t="n">
+      <c r="N118" s="20" t="n">
         <v>569.396</v>
       </c>
-      <c r="V112" s="20" t="n">
+      <c r="V118" s="20" t="n">
         <v>304.565</v>
       </c>
-      <c r="W112" s="20" t="n">
+      <c r="W118" s="20" t="n">
         <v>494.428</v>
       </c>
-      <c r="X112" s="20" t="n">
+      <c r="X118" s="20" t="n">
         <v>569.396</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C113" s="20" t="n">
-        <v>303.07</v>
-      </c>
-      <c r="D113" s="20" t="n">
-        <v>253.889</v>
-      </c>
-      <c r="E113" s="20" t="n">
-        <v>317.837</v>
-      </c>
-      <c r="F113" s="20" t="n">
-        <v>304.565</v>
-      </c>
-      <c r="G113" s="20" t="n">
-        <v>339.653</v>
-      </c>
-      <c r="H113" s="20" t="n">
-        <v>388.101</v>
-      </c>
-      <c r="I113" s="20" t="n">
-        <v>430.888</v>
-      </c>
-      <c r="J113" s="20" t="n">
-        <v>494.428</v>
-      </c>
-      <c r="K113" s="20" t="n">
-        <v>515.058</v>
-      </c>
-      <c r="L113" s="20" t="n">
-        <v>512.7910000000001</v>
-      </c>
-      <c r="M113" s="20" t="n">
-        <v>536.706</v>
-      </c>
-      <c r="N113" s="20" t="n">
-        <v>569.396</v>
-      </c>
-      <c r="V113" s="20" t="n">
-        <v>304.565</v>
-      </c>
-      <c r="W113" s="20" t="n">
-        <v>494.428</v>
-      </c>
-      <c r="X113" s="20" t="n">
-        <v>569.396</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t>기타 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C114" s="20" t="n">
-        <v>1.374</v>
-      </c>
-      <c r="D114" s="20" t="n">
-        <v>1.374</v>
-      </c>
-      <c r="E114" s="20" t="n">
-        <v>1.341</v>
-      </c>
-      <c r="F114" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="G114" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="H114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="K114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="L114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="M114" s="20" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="N114" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V114" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="W114" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="X114" s="20" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
-        <is>
-          <t>합계 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C115" s="20" t="n">
-        <v>304.444</v>
-      </c>
-      <c r="D115" s="20" t="n">
-        <v>255.263</v>
-      </c>
-      <c r="E115" s="20" t="n">
-        <v>319.179</v>
-      </c>
-      <c r="F115" s="20" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="G115" s="20" t="n">
-        <v>340.978</v>
-      </c>
-      <c r="H115" s="20" t="n">
-        <v>388.176</v>
-      </c>
-      <c r="I115" s="20" t="n">
-        <v>430.963</v>
-      </c>
-      <c r="J115" s="20" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="K115" s="20" t="n">
-        <v>515.133</v>
-      </c>
-      <c r="L115" s="20" t="n">
-        <v>512.866</v>
-      </c>
-      <c r="M115" s="20" t="n">
-        <v>536.773</v>
-      </c>
-      <c r="N115" s="20" t="n">
-        <v>569.446</v>
-      </c>
-      <c r="V115" s="20" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="W115" s="20" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="X115" s="20" t="n">
-        <v>569.446</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="18" t="inlineStr">
-        <is>
-          <t>EntityTotalMember · 외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="G117" s="20" t="n">
-        <v>340.978</v>
-      </c>
-      <c r="K117" s="20" t="n">
-        <v>515.133</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>외부 고객 매출</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n">
-        <v>304.444</v>
-      </c>
-      <c r="D118" s="12" t="n">
-        <v>255.263</v>
-      </c>
-      <c r="E118" s="12" t="n">
-        <v>319.179</v>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="G118" s="12" t="n">
-        <v>340.978</v>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>388.176</v>
-      </c>
-      <c r="I118" s="12" t="n">
-        <v>430.963</v>
-      </c>
-      <c r="J118" s="12" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="V118" s="12" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="W118" s="12" t="n">
-        <v>494.503</v>
-      </c>
-    </row>
     <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>BuddycomBusinessReportableSegmentMember · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="20" t="n">
-        <v>0</v>
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G119" s="15">
+        <f>IF(OR(G118="",C118=""),"",IF(C118&lt;=0,"",IFERROR(G118/C118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H119" s="15">
+        <f>IF(OR(H118="",D118=""),"",IF(D118&lt;=0,"",IFERROR(H118/D118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I119" s="15">
+        <f>IF(OR(I118="",E118=""),"",IF(E118&lt;=0,"",IFERROR(I118/E118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J119" s="15">
+        <f>IF(OR(J118="",F118=""),"",IF(F118&lt;=0,"",IFERROR(J118/F118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K119" s="15">
+        <f>IF(OR(K118="",G118=""),"",IF(G118&lt;=0,"",IFERROR(K118/G118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L119" s="15">
+        <f>IF(OR(L118="",H118=""),"",IF(H118&lt;=0,"",IFERROR(L118/H118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M119" s="15">
+        <f>IF(OR(M118="",I118=""),"",IF(I118&lt;=0,"",IFERROR(M118/I118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N119" s="15">
+        <f>IF(OR(N118="",J118=""),"",IF(J118&lt;=0,"",IFERROR(N118/J118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V119" s="15">
+        <f>IF(OR(V118="",U118=""),"",IF(U118&lt;=0,"",IFERROR(V118/U118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W119" s="15">
+        <f>IF(OR(W118="",V118=""),"",IF(V118&lt;=0,"",IFERROR(W118/V118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X119" s="15">
+        <f>IF(OR(X118="",W118=""),"",IF(W118&lt;=0,"",IFERROR(X118/W118-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
+          <t>보고부문 합계 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C120" s="20" t="n">
-        <v>0</v>
+        <v>303.07</v>
       </c>
       <c r="D120" s="20" t="n">
-        <v>0</v>
+        <v>253.889</v>
       </c>
       <c r="E120" s="20" t="n">
-        <v>0</v>
+        <v>317.837</v>
       </c>
       <c r="F120" s="20" t="n">
-        <v>0</v>
+        <v>304.565</v>
       </c>
       <c r="G120" s="20" t="n">
-        <v>0</v>
+        <v>339.653</v>
       </c>
       <c r="H120" s="20" t="n">
-        <v>0</v>
+        <v>388.101</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0</v>
+        <v>430.888</v>
       </c>
       <c r="J120" s="20" t="n">
-        <v>0</v>
+        <v>494.428</v>
       </c>
       <c r="K120" s="20" t="n">
-        <v>0</v>
+        <v>515.058</v>
       </c>
       <c r="L120" s="20" t="n">
-        <v>0</v>
+        <v>512.7910000000001</v>
       </c>
       <c r="M120" s="20" t="n">
-        <v>0</v>
+        <v>536.706</v>
       </c>
       <c r="N120" s="20" t="n">
-        <v>0</v>
+        <v>569.396</v>
       </c>
       <c r="V120" s="20" t="n">
-        <v>0</v>
+        <v>304.565</v>
       </c>
       <c r="W120" s="20" t="n">
-        <v>0</v>
+        <v>494.428</v>
       </c>
       <c r="X120" s="20" t="n">
-        <v>0</v>
+        <v>569.396</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="18" t="inlineStr">
-        <is>
-          <t>기타 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" s="20" t="n">
-        <v>0</v>
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G121" s="15">
+        <f>IF(OR(G120="",C120=""),"",IF(C120&lt;=0,"",IFERROR(G120/C120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H121" s="15">
+        <f>IF(OR(H120="",D120=""),"",IF(D120&lt;=0,"",IFERROR(H120/D120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I121" s="15">
+        <f>IF(OR(I120="",E120=""),"",IF(E120&lt;=0,"",IFERROR(I120/E120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J121" s="15">
+        <f>IF(OR(J120="",F120=""),"",IF(F120&lt;=0,"",IFERROR(J120/F120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K121" s="15">
+        <f>IF(OR(K120="",G120=""),"",IF(G120&lt;=0,"",IFERROR(K120/G120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L121" s="15">
+        <f>IF(OR(L120="",H120=""),"",IF(H120&lt;=0,"",IFERROR(L120/H120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M121" s="15">
+        <f>IF(OR(M120="",I120=""),"",IF(I120&lt;=0,"",IFERROR(M120/I120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N121" s="15">
+        <f>IF(OR(N120="",J120=""),"",IF(J120&lt;=0,"",IFERROR(N120/J120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V121" s="15">
+        <f>IF(OR(V120="",U120=""),"",IF(U120&lt;=0,"",IFERROR(V120/U120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W121" s="15">
+        <f>IF(OR(W120="",V120=""),"",IF(V120&lt;=0,"",IFERROR(W120/V120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X121" s="15">
+        <f>IF(OR(X120="",W120=""),"",IF(W120&lt;=0,"",IFERROR(X120/W120-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>합계 · 부문 간 내부매출·대체</t>
+          <t>기타 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C122" s="20" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="D122" s="20" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="E122" s="20" t="n">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="F122" s="20" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="G122" s="20" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="H122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="J122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="K122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="L122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="M122" s="20" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="N122" s="20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="V122" s="20" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="W122" s="20" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="X122" s="20" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · 부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" s="20" t="n">
-        <v>0</v>
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G123" s="15">
+        <f>IF(OR(G122="",C122=""),"",IF(C122&lt;=0,"",IFERROR(G122/C122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H123" s="15">
+        <f>IF(OR(H122="",D122=""),"",IF(D122&lt;=0,"",IFERROR(H122/D122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I123" s="15">
+        <f>IF(OR(I122="",E122=""),"",IF(E122&lt;=0,"",IFERROR(I122/E122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J123" s="15">
+        <f>IF(OR(J122="",F122=""),"",IF(F122&lt;=0,"",IFERROR(J122/F122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K123" s="15">
+        <f>IF(OR(K122="",G122=""),"",IF(G122&lt;=0,"",IFERROR(K122/G122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L123" s="15">
+        <f>IF(OR(L122="",H122=""),"",IF(H122&lt;=0,"",IFERROR(L122/H122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M123" s="15">
+        <f>IF(OR(M122="",I122=""),"",IF(I122&lt;=0,"",IFERROR(M122/I122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N123" s="15">
+        <f>IF(OR(N122="",J122=""),"",IF(J122&lt;=0,"",IFERROR(N122/J122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V123" s="15">
+        <f>IF(OR(V122="",U122=""),"",IF(U122&lt;=0,"",IFERROR(V122/U122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W123" s="15">
+        <f>IF(OR(W122="",V122=""),"",IF(V122&lt;=0,"",IFERROR(W122/V122-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X123" s="15">
+        <f>IF(OR(X122="",W122=""),"",IF(W122&lt;=0,"",IFERROR(X122/W122-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · 부문 간 내부매출·대체</t>
-        </is>
+          <t>합계 · 외부 고객 매출</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="n">
+        <v>304.444</v>
+      </c>
+      <c r="D124" s="20" t="n">
+        <v>255.263</v>
+      </c>
+      <c r="E124" s="20" t="n">
+        <v>319.179</v>
+      </c>
+      <c r="F124" s="20" t="n">
+        <v>305.889</v>
       </c>
       <c r="G124" s="20" t="n">
-        <v>0</v>
+        <v>340.978</v>
+      </c>
+      <c r="H124" s="20" t="n">
+        <v>388.176</v>
+      </c>
+      <c r="I124" s="20" t="n">
+        <v>430.963</v>
+      </c>
+      <c r="J124" s="20" t="n">
+        <v>494.503</v>
       </c>
       <c r="K124" s="20" t="n">
-        <v>0</v>
+        <v>515.133</v>
+      </c>
+      <c r="L124" s="20" t="n">
+        <v>512.866</v>
+      </c>
+      <c r="M124" s="20" t="n">
+        <v>536.773</v>
+      </c>
+      <c r="N124" s="20" t="n">
+        <v>569.446</v>
+      </c>
+      <c r="V124" s="20" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="W124" s="20" t="n">
+        <v>494.503</v>
+      </c>
+      <c r="X124" s="20" t="n">
+        <v>569.446</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="18" t="inlineStr">
-        <is>
-          <t>부문 간 내부매출·대체</t>
-        </is>
-      </c>
-      <c r="C125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" s="20" t="n">
-        <v>0</v>
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G125" s="15">
+        <f>IF(OR(G124="",C124=""),"",IF(C124&lt;=0,"",IFERROR(G124/C124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H125" s="15">
+        <f>IF(OR(H124="",D124=""),"",IF(D124&lt;=0,"",IFERROR(H124/D124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I125" s="15">
+        <f>IF(OR(I124="",E124=""),"",IF(E124&lt;=0,"",IFERROR(I124/E124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J125" s="15">
+        <f>IF(OR(J124="",F124=""),"",IF(F124&lt;=0,"",IFERROR(J124/F124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K125" s="15">
+        <f>IF(OR(K124="",G124=""),"",IF(G124&lt;=0,"",IFERROR(K124/G124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L125" s="15">
+        <f>IF(OR(L124="",H124=""),"",IF(H124&lt;=0,"",IFERROR(L124/H124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M125" s="15">
+        <f>IF(OR(M124="",I124=""),"",IF(I124&lt;=0,"",IFERROR(M124/I124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N125" s="15">
+        <f>IF(OR(N124="",J124=""),"",IF(J124&lt;=0,"",IFERROR(N124/J124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V125" s="15">
+        <f>IF(OR(V124="",U124=""),"",IF(U124&lt;=0,"",IFERROR(V124/U124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W125" s="15">
+        <f>IF(OR(W124="",V124=""),"",IF(V124&lt;=0,"",IFERROR(W124/V124-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X125" s="15">
+        <f>IF(OR(X124="",W124=""),"",IF(W124&lt;=0,"",IFERROR(X124/W124-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>BuddycomBusinessReportableSegmentMember · 계</t>
+          <t>조정액 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C126" s="20" t="n">
-        <v>303.07</v>
+        <v>0</v>
       </c>
       <c r="D126" s="20" t="n">
-        <v>253.889</v>
+        <v>0</v>
       </c>
       <c r="E126" s="20" t="n">
-        <v>317.837</v>
+        <v>0</v>
       </c>
       <c r="F126" s="20" t="n">
-        <v>304.565</v>
+        <v>0</v>
       </c>
       <c r="G126" s="20" t="n">
-        <v>339.653</v>
+        <v>0</v>
       </c>
       <c r="H126" s="20" t="n">
-        <v>388.101</v>
+        <v>0</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>430.888</v>
+        <v>0</v>
       </c>
       <c r="J126" s="20" t="n">
-        <v>494.428</v>
+        <v>0</v>
       </c>
       <c r="K126" s="20" t="n">
-        <v>515.058</v>
+        <v>0</v>
       </c>
       <c r="L126" s="20" t="n">
-        <v>512.7910000000001</v>
+        <v>0</v>
       </c>
       <c r="M126" s="20" t="n">
-        <v>536.706</v>
+        <v>0</v>
       </c>
       <c r="N126" s="20" t="n">
-        <v>569.396</v>
+        <v>0</v>
       </c>
       <c r="V126" s="20" t="n">
-        <v>304.565</v>
+        <v>0</v>
       </c>
       <c r="W126" s="20" t="n">
-        <v>494.428</v>
+        <v>0</v>
       </c>
       <c r="X126" s="20" t="n">
-        <v>569.396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 계</t>
-        </is>
-      </c>
-      <c r="C127" s="20" t="n">
-        <v>303.07</v>
-      </c>
-      <c r="D127" s="20" t="n">
-        <v>253.889</v>
-      </c>
-      <c r="E127" s="20" t="n">
-        <v>317.837</v>
-      </c>
-      <c r="F127" s="20" t="n">
-        <v>304.565</v>
+          <t>EntityTotalMember · 외부 고객 매출</t>
+        </is>
       </c>
       <c r="G127" s="20" t="n">
-        <v>339.653</v>
-      </c>
-      <c r="H127" s="20" t="n">
-        <v>388.101</v>
-      </c>
-      <c r="I127" s="20" t="n">
-        <v>430.888</v>
-      </c>
-      <c r="J127" s="20" t="n">
-        <v>494.428</v>
+        <v>340.978</v>
       </c>
       <c r="K127" s="20" t="n">
-        <v>515.058</v>
-      </c>
-      <c r="L127" s="20" t="n">
-        <v>512.7910000000001</v>
-      </c>
-      <c r="M127" s="20" t="n">
-        <v>536.706</v>
-      </c>
-      <c r="N127" s="20" t="n">
-        <v>569.396</v>
-      </c>
-      <c r="V127" s="20" t="n">
-        <v>304.565</v>
-      </c>
-      <c r="W127" s="20" t="n">
-        <v>494.428</v>
-      </c>
-      <c r="X127" s="20" t="n">
-        <v>569.396</v>
+        <v>515.133</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="18" t="inlineStr">
-        <is>
-          <t>기타 · 계</t>
-        </is>
-      </c>
-      <c r="C128" s="20" t="n">
-        <v>1.374</v>
-      </c>
-      <c r="D128" s="20" t="n">
-        <v>1.374</v>
-      </c>
-      <c r="E128" s="20" t="n">
-        <v>1.341</v>
-      </c>
-      <c r="F128" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="G128" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="H128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="K128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="L128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="M128" s="20" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="N128" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V128" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="W128" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="X128" s="20" t="n">
-        <v>0.05</v>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>외부 고객 매출</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>304.444</v>
+      </c>
+      <c r="D128" s="12" t="n">
+        <v>255.263</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>319.179</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>340.978</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>388.176</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>430.963</v>
+      </c>
+      <c r="J128" s="12" t="n">
+        <v>494.503</v>
+      </c>
+      <c r="V128" s="12" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="W128" s="12" t="n">
+        <v>494.503</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="18" t="inlineStr">
-        <is>
-          <t>합계 · 계</t>
-        </is>
-      </c>
-      <c r="C129" s="20" t="n">
-        <v>304.444</v>
-      </c>
-      <c r="D129" s="20" t="n">
-        <v>255.263</v>
-      </c>
-      <c r="E129" s="20" t="n">
-        <v>319.179</v>
-      </c>
-      <c r="F129" s="20" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="G129" s="20" t="n">
-        <v>340.978</v>
-      </c>
-      <c r="H129" s="20" t="n">
-        <v>388.176</v>
-      </c>
-      <c r="I129" s="20" t="n">
-        <v>430.963</v>
-      </c>
-      <c r="J129" s="20" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="K129" s="20" t="n">
-        <v>515.133</v>
-      </c>
-      <c r="L129" s="20" t="n">
-        <v>512.866</v>
-      </c>
-      <c r="M129" s="20" t="n">
-        <v>536.773</v>
-      </c>
-      <c r="N129" s="20" t="n">
-        <v>569.446</v>
-      </c>
-      <c r="V129" s="20" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="W129" s="20" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="X129" s="20" t="n">
-        <v>569.446</v>
+      <c r="A129" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G129" s="15">
+        <f>IF(OR(G128="",C128=""),"",IF(C128&lt;=0,"",IFERROR(G128/C128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H129" s="15">
+        <f>IF(OR(H128="",D128=""),"",IF(D128&lt;=0,"",IFERROR(H128/D128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I129" s="15">
+        <f>IF(OR(I128="",E128=""),"",IF(E128&lt;=0,"",IFERROR(I128/E128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J129" s="15">
+        <f>IF(OR(J128="",F128=""),"",IF(F128&lt;=0,"",IFERROR(J128/F128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V129" s="15">
+        <f>IF(OR(V128="",U128=""),"",IF(U128&lt;=0,"",IFERROR(V128/U128-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W129" s="15">
+        <f>IF(OR(W128="",V128=""),"",IF(V128&lt;=0,"",IFERROR(W128/V128-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 계</t>
+          <t>BuddycomBusinessReportableSegmentMember · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C130" s="20" t="n">
@@ -8485,2030 +8630,2527 @@
     <row r="131">
       <c r="A131" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · 계</t>
-        </is>
+          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="C131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="20" t="n">
-        <v>340.978</v>
+        <v>0</v>
+      </c>
+      <c r="H131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="K131" s="20" t="n">
-        <v>515.133</v>
+        <v>0</v>
+      </c>
+      <c r="L131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="n">
-        <v>304.444</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>255.263</v>
-      </c>
-      <c r="E132" s="12" t="n">
-        <v>319.179</v>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>340.978</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>388.176</v>
-      </c>
-      <c r="I132" s="12" t="n">
-        <v>430.963</v>
-      </c>
-      <c r="J132" s="12" t="n">
-        <v>494.503</v>
-      </c>
-      <c r="V132" s="12" t="n">
-        <v>305.889</v>
-      </c>
-      <c r="W132" s="12" t="n">
-        <v>494.503</v>
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>기타 · 부문 간 내부매출·대체</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>BuddycomBusinessReportableSegmentMember · 부문 이익</t>
+          <t>합계 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
-        <v>-21.655</v>
+        <v>0</v>
       </c>
       <c r="D133" s="20" t="n">
-        <v>3.962</v>
+        <v>0</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>-21.286</v>
+        <v>0</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>3.193</v>
+        <v>0</v>
       </c>
       <c r="G133" s="20" t="n">
-        <v>7.466</v>
+        <v>0</v>
       </c>
       <c r="H133" s="20" t="n">
-        <v>23.815</v>
+        <v>0</v>
       </c>
       <c r="I133" s="20" t="n">
-        <v>24.741</v>
+        <v>0</v>
       </c>
       <c r="J133" s="20" t="n">
-        <v>49.915</v>
+        <v>0</v>
       </c>
       <c r="K133" s="20" t="n">
-        <v>56.497</v>
+        <v>0</v>
       </c>
       <c r="L133" s="20" t="n">
-        <v>48.304</v>
+        <v>0</v>
       </c>
       <c r="M133" s="20" t="n">
-        <v>44.256</v>
+        <v>0</v>
       </c>
       <c r="N133" s="20" t="n">
-        <v>112.725</v>
+        <v>0</v>
       </c>
       <c r="V133" s="20" t="n">
-        <v>3.193</v>
+        <v>0</v>
       </c>
       <c r="W133" s="20" t="n">
-        <v>49.915</v>
+        <v>0</v>
       </c>
       <c r="X133" s="20" t="n">
-        <v>112.725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 이익</t>
+          <t>조정액 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
-        <v>-21.655</v>
+        <v>0</v>
       </c>
       <c r="D134" s="20" t="n">
-        <v>3.962</v>
+        <v>0</v>
       </c>
       <c r="E134" s="20" t="n">
-        <v>-21.286</v>
+        <v>0</v>
       </c>
       <c r="F134" s="20" t="n">
-        <v>3.193</v>
+        <v>0</v>
       </c>
       <c r="G134" s="20" t="n">
-        <v>7.466</v>
+        <v>0</v>
       </c>
       <c r="H134" s="20" t="n">
-        <v>23.815</v>
+        <v>0</v>
       </c>
       <c r="I134" s="20" t="n">
-        <v>24.741</v>
+        <v>0</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>49.915</v>
+        <v>0</v>
       </c>
       <c r="K134" s="20" t="n">
-        <v>56.497</v>
+        <v>0</v>
       </c>
       <c r="L134" s="20" t="n">
-        <v>48.304</v>
+        <v>0</v>
       </c>
       <c r="M134" s="20" t="n">
-        <v>44.256</v>
+        <v>0</v>
       </c>
       <c r="N134" s="20" t="n">
-        <v>112.725</v>
+        <v>0</v>
       </c>
       <c r="V134" s="20" t="n">
-        <v>3.193</v>
+        <v>0</v>
       </c>
       <c r="W134" s="20" t="n">
-        <v>49.915</v>
+        <v>0</v>
       </c>
       <c r="X134" s="20" t="n">
-        <v>112.725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>기타 · 부문 이익</t>
-        </is>
-      </c>
-      <c r="C135" s="20" t="n">
-        <v>1.137</v>
-      </c>
-      <c r="D135" s="20" t="n">
-        <v>1.118</v>
-      </c>
-      <c r="E135" s="20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F135" s="20" t="n">
-        <v>1.115</v>
+          <t>EntityTotalMember · 부문 간 내부매출·대체</t>
+        </is>
       </c>
       <c r="G135" s="20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H135" s="20" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="I135" s="20" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="J135" s="20" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="K135" s="20" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="L135" s="20" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="M135" s="20" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="N135" s="20" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="V135" s="20" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="W135" s="20" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="X135" s="20" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>합계 · 부문 이익</t>
+          <t>부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C136" s="20" t="n">
-        <v>-20.517</v>
+        <v>0</v>
       </c>
       <c r="D136" s="20" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="E136" s="20" t="n">
-        <v>-20.146</v>
+        <v>0</v>
       </c>
       <c r="F136" s="20" t="n">
-        <v>4.308</v>
+        <v>0</v>
       </c>
       <c r="G136" s="20" t="n">
-        <v>8.606</v>
+        <v>0</v>
       </c>
       <c r="H136" s="20" t="n">
-        <v>23.864</v>
+        <v>0</v>
       </c>
       <c r="I136" s="20" t="n">
-        <v>24.799</v>
+        <v>0</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>49.987</v>
-      </c>
-      <c r="K136" s="20" t="n">
-        <v>56.558</v>
-      </c>
-      <c r="L136" s="20" t="n">
-        <v>48.366</v>
-      </c>
-      <c r="M136" s="20" t="n">
-        <v>44.309</v>
-      </c>
-      <c r="N136" s="20" t="n">
-        <v>112.769</v>
+        <v>0</v>
       </c>
       <c r="V136" s="20" t="n">
-        <v>4.308</v>
+        <v>0</v>
       </c>
       <c r="W136" s="20" t="n">
-        <v>49.987</v>
-      </c>
-      <c r="X136" s="20" t="n">
-        <v>112.769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 부문 이익</t>
+          <t>BuddycomBusinessReportableSegmentMember · 계</t>
         </is>
       </c>
       <c r="C137" s="20" t="n">
-        <v>0</v>
+        <v>303.07</v>
       </c>
       <c r="D137" s="20" t="n">
-        <v>0</v>
+        <v>253.889</v>
       </c>
       <c r="E137" s="20" t="n">
-        <v>0</v>
+        <v>317.837</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0</v>
+        <v>304.565</v>
       </c>
       <c r="G137" s="20" t="n">
-        <v>0</v>
+        <v>339.653</v>
       </c>
       <c r="H137" s="20" t="n">
-        <v>0</v>
+        <v>388.101</v>
       </c>
       <c r="I137" s="20" t="n">
-        <v>0</v>
+        <v>430.888</v>
       </c>
       <c r="J137" s="20" t="n">
-        <v>0</v>
+        <v>494.428</v>
       </c>
       <c r="K137" s="20" t="n">
-        <v>0</v>
+        <v>515.058</v>
       </c>
       <c r="L137" s="20" t="n">
-        <v>0</v>
+        <v>512.7910000000001</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0</v>
+        <v>536.706</v>
       </c>
       <c r="N137" s="20" t="n">
-        <v>0</v>
+        <v>569.396</v>
       </c>
       <c r="V137" s="20" t="n">
-        <v>0</v>
+        <v>304.565</v>
       </c>
       <c r="W137" s="20" t="n">
-        <v>0</v>
+        <v>494.428</v>
       </c>
       <c r="X137" s="20" t="n">
-        <v>0</v>
+        <v>569.396</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>EntityTotalMember · 부문 이익</t>
-        </is>
-      </c>
-      <c r="G138" s="20" t="n">
-        <v>8.606</v>
-      </c>
-      <c r="K138" s="20" t="n">
-        <v>56.558</v>
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G138" s="15">
+        <f>IF(OR(G137="",C137=""),"",IF(C137&lt;=0,"",IFERROR(G137/C137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H138" s="15">
+        <f>IF(OR(H137="",D137=""),"",IF(D137&lt;=0,"",IFERROR(H137/D137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I138" s="15">
+        <f>IF(OR(I137="",E137=""),"",IF(E137&lt;=0,"",IFERROR(I137/E137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J138" s="15">
+        <f>IF(OR(J137="",F137=""),"",IF(F137&lt;=0,"",IFERROR(J137/F137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K138" s="15">
+        <f>IF(OR(K137="",G137=""),"",IF(G137&lt;=0,"",IFERROR(K137/G137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L138" s="15">
+        <f>IF(OR(L137="",H137=""),"",IF(H137&lt;=0,"",IFERROR(L137/H137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M138" s="15">
+        <f>IF(OR(M137="",I137=""),"",IF(I137&lt;=0,"",IFERROR(M137/I137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N138" s="15">
+        <f>IF(OR(N137="",J137=""),"",IF(J137&lt;=0,"",IFERROR(N137/J137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V138" s="15">
+        <f>IF(OR(V137="",U137=""),"",IF(U137&lt;=0,"",IFERROR(V137/U137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W138" s="15">
+        <f>IF(OR(W137="",V137=""),"",IF(V137&lt;=0,"",IFERROR(W137/V137-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X138" s="15">
+        <f>IF(OR(X137="",W137=""),"",IF(W137&lt;=0,"",IFERROR(X137/W137-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>부문 이익</t>
-        </is>
-      </c>
-      <c r="C139" s="12" t="n">
-        <v>-20.517</v>
-      </c>
-      <c r="D139" s="12" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="E139" s="12" t="n">
-        <v>-20.146</v>
-      </c>
-      <c r="F139" s="12" t="n">
-        <v>4.308</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>8.606</v>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>23.864</v>
-      </c>
-      <c r="I139" s="12" t="n">
-        <v>24.799</v>
-      </c>
-      <c r="J139" s="12" t="n">
-        <v>49.987</v>
-      </c>
-      <c r="V139" s="12" t="n">
-        <v>4.308</v>
-      </c>
-      <c r="W139" s="12" t="n">
-        <v>49.987</v>
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>보고부문 합계 · 계</t>
+        </is>
+      </c>
+      <c r="C139" s="20" t="n">
+        <v>303.07</v>
+      </c>
+      <c r="D139" s="20" t="n">
+        <v>253.889</v>
+      </c>
+      <c r="E139" s="20" t="n">
+        <v>317.837</v>
+      </c>
+      <c r="F139" s="20" t="n">
+        <v>304.565</v>
+      </c>
+      <c r="G139" s="20" t="n">
+        <v>339.653</v>
+      </c>
+      <c r="H139" s="20" t="n">
+        <v>388.101</v>
+      </c>
+      <c r="I139" s="20" t="n">
+        <v>430.888</v>
+      </c>
+      <c r="J139" s="20" t="n">
+        <v>494.428</v>
+      </c>
+      <c r="K139" s="20" t="n">
+        <v>515.058</v>
+      </c>
+      <c r="L139" s="20" t="n">
+        <v>512.7910000000001</v>
+      </c>
+      <c r="M139" s="20" t="n">
+        <v>536.706</v>
+      </c>
+      <c r="N139" s="20" t="n">
+        <v>569.396</v>
+      </c>
+      <c r="V139" s="20" t="n">
+        <v>304.565</v>
+      </c>
+      <c r="W139" s="20" t="n">
+        <v>494.428</v>
+      </c>
+      <c r="X139" s="20" t="n">
+        <v>569.396</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G140" s="15">
+        <f>IF(OR(G139="",C139=""),"",IF(C139&lt;=0,"",IFERROR(G139/C139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H140" s="15">
+        <f>IF(OR(H139="",D139=""),"",IF(D139&lt;=0,"",IFERROR(H139/D139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I140" s="15">
+        <f>IF(OR(I139="",E139=""),"",IF(E139&lt;=0,"",IFERROR(I139/E139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J140" s="15">
+        <f>IF(OR(J139="",F139=""),"",IF(F139&lt;=0,"",IFERROR(J139/F139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K140" s="15">
+        <f>IF(OR(K139="",G139=""),"",IF(G139&lt;=0,"",IFERROR(K139/G139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L140" s="15">
+        <f>IF(OR(L139="",H139=""),"",IF(H139&lt;=0,"",IFERROR(L139/H139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M140" s="15">
+        <f>IF(OR(M139="",I139=""),"",IF(I139&lt;=0,"",IFERROR(M139/I139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N140" s="15">
+        <f>IF(OR(N139="",J139=""),"",IF(J139&lt;=0,"",IFERROR(N139/J139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V140" s="15">
+        <f>IF(OR(V139="",U139=""),"",IF(U139&lt;=0,"",IFERROR(V139/U139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W140" s="15">
+        <f>IF(OR(W139="",V139=""),"",IF(V139&lt;=0,"",IFERROR(W139/V139-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X140" s="15">
+        <f>IF(OR(X139="",W139=""),"",IF(W139&lt;=0,"",IFERROR(X139/W139-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="16" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B141" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C141" s="16" t="n"/>
-      <c r="D141" s="16" t="n"/>
-      <c r="E141" s="16" t="n"/>
-      <c r="F141" s="16" t="n"/>
-      <c r="G141" s="16" t="n"/>
-      <c r="H141" s="16" t="n"/>
-      <c r="I141" s="16" t="n"/>
-      <c r="J141" s="16" t="n"/>
-      <c r="K141" s="16" t="n"/>
-      <c r="L141" s="16" t="n"/>
-      <c r="M141" s="16" t="n"/>
-      <c r="N141" s="16" t="n"/>
-      <c r="O141" s="16" t="n"/>
-      <c r="P141" s="16" t="n"/>
-      <c r="Q141" s="16" t="n"/>
-      <c r="R141" s="16" t="n"/>
-      <c r="S141" s="16" t="n"/>
-      <c r="T141" s="16" t="n"/>
-      <c r="U141" s="16" t="n"/>
-      <c r="V141" s="16" t="n"/>
-      <c r="W141" s="16" t="n"/>
-      <c r="X141" s="16" t="n"/>
-      <c r="Y141" s="16" t="n"/>
-      <c r="Z141" s="16" t="n"/>
-      <c r="AA141" s="16" t="n"/>
-      <c r="AB141" s="16" t="n"/>
-      <c r="AC141" s="16" t="n"/>
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>기타 · 계</t>
+        </is>
+      </c>
+      <c r="C141" s="20" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="D141" s="20" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="E141" s="20" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="F141" s="20" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="G141" s="20" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="H141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="L141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M141" s="20" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="N141" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V141" s="20" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="W141" s="20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="X141" s="20" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>2024.1Q</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="J142" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="K142" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="L142" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="N142" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="O142" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P142" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q142" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R142" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S142" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T142" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U142" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V142" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W142" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X142" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y142" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z142" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA142" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB142" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC142" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G142" s="15">
+        <f>IF(OR(G141="",C141=""),"",IF(C141&lt;=0,"",IFERROR(G141/C141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H142" s="15">
+        <f>IF(OR(H141="",D141=""),"",IF(D141&lt;=0,"",IFERROR(H141/D141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I142" s="15">
+        <f>IF(OR(I141="",E141=""),"",IF(E141&lt;=0,"",IFERROR(I141/E141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J142" s="15">
+        <f>IF(OR(J141="",F141=""),"",IF(F141&lt;=0,"",IFERROR(J141/F141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K142" s="15">
+        <f>IF(OR(K141="",G141=""),"",IF(G141&lt;=0,"",IFERROR(K141/G141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L142" s="15">
+        <f>IF(OR(L141="",H141=""),"",IF(H141&lt;=0,"",IFERROR(L141/H141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M142" s="15">
+        <f>IF(OR(M141="",I141=""),"",IF(I141&lt;=0,"",IFERROR(M141/I141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N142" s="15">
+        <f>IF(OR(N141="",J141=""),"",IF(J141&lt;=0,"",IFERROR(N141/J141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V142" s="15">
+        <f>IF(OR(V141="",U141=""),"",IF(U141&lt;=0,"",IFERROR(V141/U141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W142" s="15">
+        <f>IF(OR(W141="",V141=""),"",IF(V141&lt;=0,"",IFERROR(W141/V141-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X142" s="15">
+        <f>IF(OR(X141="",W141=""),"",IF(W141&lt;=0,"",IFERROR(X141/W141-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="D143" s="12" t="n">
-        <v>-16.988</v>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>17.439</v>
-      </c>
-      <c r="J143" s="12" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="L143" s="12" t="n">
-        <v>103.292</v>
-      </c>
-      <c r="N143" s="12" t="n">
-        <v>262.775</v>
-      </c>
-      <c r="S143" s="12" t="n">
-        <v>-95.666</v>
-      </c>
-      <c r="T143" s="12" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="U143" s="12" t="n">
-        <v>-72.468</v>
-      </c>
-      <c r="V143" s="12" t="n">
-        <v>-34</v>
-      </c>
-      <c r="W143" s="12" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="X143" s="12" t="n">
-        <v>262.775</v>
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>합계 · 계</t>
+        </is>
+      </c>
+      <c r="C143" s="20" t="n">
+        <v>304.444</v>
+      </c>
+      <c r="D143" s="20" t="n">
+        <v>255.263</v>
+      </c>
+      <c r="E143" s="20" t="n">
+        <v>319.179</v>
+      </c>
+      <c r="F143" s="20" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="G143" s="20" t="n">
+        <v>340.978</v>
+      </c>
+      <c r="H143" s="20" t="n">
+        <v>388.176</v>
+      </c>
+      <c r="I143" s="20" t="n">
+        <v>430.963</v>
+      </c>
+      <c r="J143" s="20" t="n">
+        <v>494.503</v>
+      </c>
+      <c r="K143" s="20" t="n">
+        <v>515.133</v>
+      </c>
+      <c r="L143" s="20" t="n">
+        <v>512.866</v>
+      </c>
+      <c r="M143" s="20" t="n">
+        <v>536.773</v>
+      </c>
+      <c r="N143" s="20" t="n">
+        <v>569.446</v>
+      </c>
+      <c r="V143" s="20" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="W143" s="20" t="n">
+        <v>494.503</v>
+      </c>
+      <c r="X143" s="20" t="n">
+        <v>569.446</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="18" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="D144" s="20" t="n">
-        <v>6.718</v>
-      </c>
-      <c r="F144" s="20" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="H144" s="20" t="n">
-        <v>7.239</v>
-      </c>
-      <c r="J144" s="20" t="n">
-        <v>15.884</v>
-      </c>
-      <c r="L144" s="20" t="n">
-        <v>28.413</v>
-      </c>
-      <c r="N144" s="20" t="n">
-        <v>28.641</v>
-      </c>
-      <c r="S144" s="20" t="n">
-        <v>1.594</v>
-      </c>
-      <c r="T144" s="20" t="n">
-        <v>3.997</v>
-      </c>
-      <c r="U144" s="20" t="n">
-        <v>21.665</v>
-      </c>
-      <c r="V144" s="20" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="W144" s="20" t="n">
-        <v>15.884</v>
-      </c>
-      <c r="X144" s="20" t="n">
-        <v>28.641</v>
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G144" s="15">
+        <f>IF(OR(G143="",C143=""),"",IF(C143&lt;=0,"",IFERROR(G143/C143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H144" s="15">
+        <f>IF(OR(H143="",D143=""),"",IF(D143&lt;=0,"",IFERROR(H143/D143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I144" s="15">
+        <f>IF(OR(I143="",E143=""),"",IF(E143&lt;=0,"",IFERROR(I143/E143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J144" s="15">
+        <f>IF(OR(J143="",F143=""),"",IF(F143&lt;=0,"",IFERROR(J143/F143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K144" s="15">
+        <f>IF(OR(K143="",G143=""),"",IF(G143&lt;=0,"",IFERROR(K143/G143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L144" s="15">
+        <f>IF(OR(L143="",H143=""),"",IF(H143&lt;=0,"",IFERROR(L143/H143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M144" s="15">
+        <f>IF(OR(M143="",I143=""),"",IF(I143&lt;=0,"",IFERROR(M143/I143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N144" s="15">
+        <f>IF(OR(N143="",J143=""),"",IF(J143&lt;=0,"",IFERROR(N143/J143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V144" s="15">
+        <f>IF(OR(V143="",U143=""),"",IF(U143&lt;=0,"",IFERROR(V143/U143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W144" s="15">
+        <f>IF(OR(W143="",V143=""),"",IF(V143&lt;=0,"",IFERROR(W143/V143-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X144" s="15">
+        <f>IF(OR(X143="",W143=""),"",IF(W143&lt;=0,"",IFERROR(X143/W143-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
-        </is>
+          <t>조정액 · 계</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H145" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="I145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="L145" s="20" t="n">
-        <v>7.326</v>
+        <v>0</v>
+      </c>
+      <c r="M145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="D146" s="20" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="F146" s="20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H146" s="20" t="n">
-        <v>-0.513</v>
-      </c>
-      <c r="J146" s="20" t="n">
-        <v>-1.942</v>
-      </c>
-      <c r="L146" s="20" t="n">
-        <v>-1.706</v>
-      </c>
-      <c r="N146" s="20" t="n">
-        <v>-3.609</v>
-      </c>
-      <c r="S146" s="20" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="T146" s="20" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="U146" s="20" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="V146" s="20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="W146" s="20" t="n">
-        <v>-1.942</v>
-      </c>
-      <c r="X146" s="20" t="n">
-        <v>-3.609</v>
+          <t>EntityTotalMember · 계</t>
+        </is>
+      </c>
+      <c r="G146" s="20" t="n">
+        <v>340.978</v>
+      </c>
+      <c r="K146" s="20" t="n">
+        <v>515.133</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="D147" s="20" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F147" s="20" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" s="20" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="W147" s="20" t="n">
-        <v>0</v>
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="n">
+        <v>304.444</v>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>255.263</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>319.179</v>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>340.978</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>388.176</v>
+      </c>
+      <c r="I147" s="12" t="n">
+        <v>430.963</v>
+      </c>
+      <c r="J147" s="12" t="n">
+        <v>494.503</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>305.889</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>494.503</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>유가증권 이자</t>
-        </is>
-      </c>
-      <c r="J148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" s="20" t="n">
-        <v>-1.426</v>
-      </c>
-      <c r="W148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" s="20" t="n">
-        <v>-1.426</v>
+      <c r="A148" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G148" s="15">
+        <f>IF(OR(G147="",C147=""),"",IF(C147&lt;=0,"",IFERROR(G147/C147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H148" s="15">
+        <f>IF(OR(H147="",D147=""),"",IF(D147&lt;=0,"",IFERROR(H147/D147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I148" s="15">
+        <f>IF(OR(I147="",E147=""),"",IF(E147&lt;=0,"",IFERROR(I147/E147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J148" s="15">
+        <f>IF(OR(J147="",F147=""),"",IF(F147&lt;=0,"",IFERROR(J147/F147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V148" s="15">
+        <f>IF(OR(V147="",U147=""),"",IF(U147&lt;=0,"",IFERROR(V147/U147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W148" s="15">
+        <f>IF(OR(W147="",V147=""),"",IF(V147&lt;=0,"",IFERROR(W147/V147-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
+          <t>BuddycomBusinessReportableSegmentMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="n">
+        <v>-21.655</v>
+      </c>
+      <c r="D149" s="20" t="n">
+        <v>3.962</v>
+      </c>
+      <c r="E149" s="20" t="n">
+        <v>-21.286</v>
       </c>
       <c r="F149" s="20" t="n">
-        <v>0.004</v>
+        <v>3.193</v>
+      </c>
+      <c r="G149" s="20" t="n">
+        <v>7.466</v>
+      </c>
+      <c r="H149" s="20" t="n">
+        <v>23.815</v>
+      </c>
+      <c r="I149" s="20" t="n">
+        <v>24.741</v>
       </c>
       <c r="J149" s="20" t="n">
-        <v>-0.001</v>
+        <v>49.915</v>
+      </c>
+      <c r="K149" s="20" t="n">
+        <v>56.497</v>
+      </c>
+      <c r="L149" s="20" t="n">
+        <v>48.304</v>
+      </c>
+      <c r="M149" s="20" t="n">
+        <v>44.256</v>
       </c>
       <c r="N149" s="20" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="U149" s="20" t="n">
-        <v>0</v>
+        <v>112.725</v>
       </c>
       <c r="V149" s="20" t="n">
-        <v>0.004</v>
+        <v>3.193</v>
       </c>
       <c r="W149" s="20" t="n">
-        <v>-0.001</v>
+        <v>49.915</v>
       </c>
       <c r="X149" s="20" t="n">
-        <v>-0.006</v>
+        <v>112.725</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="18" t="inlineStr">
-        <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="D150" s="20" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="F150" s="20" t="n">
-        <v>1.619</v>
-      </c>
-      <c r="H150" s="20" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J150" s="20" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="L150" s="20" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="N150" s="20" t="n">
-        <v>1.325</v>
-      </c>
-      <c r="S150" s="20" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="T150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="20" t="n">
-        <v>1.619</v>
-      </c>
-      <c r="W150" s="20" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="X150" s="20" t="n">
-        <v>1.325</v>
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C150" s="15">
+        <f>IF(OR(C149="",C137=""),"",IF(C137&lt;=0,"",IFERROR(C149/C137,"")))</f>
+        <v/>
+      </c>
+      <c r="D150" s="15">
+        <f>IF(OR(D149="",D137=""),"",IF(D137&lt;=0,"",IFERROR(D149/D137,"")))</f>
+        <v/>
+      </c>
+      <c r="E150" s="15">
+        <f>IF(OR(E149="",E137=""),"",IF(E137&lt;=0,"",IFERROR(E149/E137,"")))</f>
+        <v/>
+      </c>
+      <c r="F150" s="15">
+        <f>IF(OR(F149="",F137=""),"",IF(F137&lt;=0,"",IFERROR(F149/F137,"")))</f>
+        <v/>
+      </c>
+      <c r="G150" s="15">
+        <f>IF(OR(G149="",G137=""),"",IF(G137&lt;=0,"",IFERROR(G149/G137,"")))</f>
+        <v/>
+      </c>
+      <c r="H150" s="15">
+        <f>IF(OR(H149="",H137=""),"",IF(H137&lt;=0,"",IFERROR(H149/H137,"")))</f>
+        <v/>
+      </c>
+      <c r="I150" s="15">
+        <f>IF(OR(I149="",I137=""),"",IF(I137&lt;=0,"",IFERROR(I149/I137,"")))</f>
+        <v/>
+      </c>
+      <c r="J150" s="15">
+        <f>IF(OR(J149="",J137=""),"",IF(J137&lt;=0,"",IFERROR(J149/J137,"")))</f>
+        <v/>
+      </c>
+      <c r="K150" s="15">
+        <f>IF(OR(K149="",K137=""),"",IF(K137&lt;=0,"",IFERROR(K149/K137,"")))</f>
+        <v/>
+      </c>
+      <c r="L150" s="15">
+        <f>IF(OR(L149="",L137=""),"",IF(L137&lt;=0,"",IFERROR(L149/L137,"")))</f>
+        <v/>
+      </c>
+      <c r="M150" s="15">
+        <f>IF(OR(M149="",M137=""),"",IF(M137&lt;=0,"",IFERROR(M149/M137,"")))</f>
+        <v/>
+      </c>
+      <c r="N150" s="15">
+        <f>IF(OR(N149="",N137=""),"",IF(N137&lt;=0,"",IFERROR(N149/N137,"")))</f>
+        <v/>
+      </c>
+      <c r="V150" s="15">
+        <f>IF(OR(V149="",V137=""),"",IF(V137&lt;=0,"",IFERROR(V149/V137,"")))</f>
+        <v/>
+      </c>
+      <c r="W150" s="15">
+        <f>IF(OR(W149="",W137=""),"",IF(W137&lt;=0,"",IFERROR(W149/W137,"")))</f>
+        <v/>
+      </c>
+      <c r="X150" s="15">
+        <f>IF(OR(X149="",X137=""),"",IF(X137&lt;=0,"",IFERROR(X149/X137,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="18" t="inlineStr">
-        <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="D151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" s="20" t="n">
-        <v>4.999</v>
-      </c>
-      <c r="V151" s="20" t="n">
-        <v>0</v>
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G151" s="15">
+        <f>IF(OR(G149="",C149=""),"",IF(C149&lt;=0,"",IFERROR(G149/C149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H151" s="15">
+        <f>IF(OR(H149="",D149=""),"",IF(D149&lt;=0,"",IFERROR(H149/D149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I151" s="15">
+        <f>IF(OR(I149="",E149=""),"",IF(E149&lt;=0,"",IFERROR(I149/E149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J151" s="15">
+        <f>IF(OR(J149="",F149=""),"",IF(F149&lt;=0,"",IFERROR(J149/F149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K151" s="15">
+        <f>IF(OR(K149="",G149=""),"",IF(G149&lt;=0,"",IFERROR(K149/G149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L151" s="15">
+        <f>IF(OR(L149="",H149=""),"",IF(H149&lt;=0,"",IFERROR(L149/H149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M151" s="15">
+        <f>IF(OR(M149="",I149=""),"",IF(I149&lt;=0,"",IFERROR(M149/I149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N151" s="15">
+        <f>IF(OR(N149="",J149=""),"",IF(J149&lt;=0,"",IFERROR(N149/J149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V151" s="15">
+        <f>IF(OR(V149="",U149=""),"",IF(U149&lt;=0,"",IFERROR(V149/U149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W151" s="15">
+        <f>IF(OR(W149="",V149=""),"",IF(V149&lt;=0,"",IFERROR(W149/V149-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X151" s="15">
+        <f>IF(OR(X149="",W149=""),"",IF(W149&lt;=0,"",IFERROR(X149/W149-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>주식교부비</t>
-        </is>
+          <t>보고부문 합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="n">
+        <v>-21.655</v>
       </c>
       <c r="D152" s="20" t="n">
-        <v>0</v>
+        <v>3.962</v>
+      </c>
+      <c r="E152" s="20" t="n">
+        <v>-21.286</v>
       </c>
       <c r="F152" s="20" t="n">
-        <v>0</v>
+        <v>3.193</v>
+      </c>
+      <c r="G152" s="20" t="n">
+        <v>7.466</v>
       </c>
       <c r="H152" s="20" t="n">
-        <v>14.011</v>
+        <v>23.815</v>
+      </c>
+      <c r="I152" s="20" t="n">
+        <v>24.741</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>14.011</v>
+        <v>49.915</v>
+      </c>
+      <c r="K152" s="20" t="n">
+        <v>56.497</v>
       </c>
       <c r="L152" s="20" t="n">
-        <v>0</v>
+        <v>48.304</v>
+      </c>
+      <c r="M152" s="20" t="n">
+        <v>44.256</v>
       </c>
       <c r="N152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" s="20" t="n">
-        <v>4.353</v>
-      </c>
-      <c r="U152" s="20" t="n">
-        <v>0</v>
+        <v>112.725</v>
       </c>
       <c r="V152" s="20" t="n">
-        <v>0</v>
+        <v>3.193</v>
       </c>
       <c r="W152" s="20" t="n">
-        <v>14.011</v>
+        <v>49.915</v>
       </c>
       <c r="X152" s="20" t="n">
-        <v>0</v>
+        <v>112.725</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="18" t="inlineStr">
-        <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="D153" s="20" t="n">
-        <v>-17.01</v>
-      </c>
-      <c r="F153" s="20" t="n">
-        <v>-35.365</v>
-      </c>
-      <c r="H153" s="20" t="n">
-        <v>-11.636</v>
-      </c>
-      <c r="J153" s="20" t="n">
-        <v>-50.145</v>
-      </c>
-      <c r="L153" s="20" t="n">
-        <v>-16.752</v>
-      </c>
-      <c r="N153" s="20" t="n">
-        <v>34.528</v>
-      </c>
-      <c r="S153" s="20" t="n">
-        <v>-35.703</v>
-      </c>
-      <c r="T153" s="20" t="n">
-        <v>10.947</v>
-      </c>
-      <c r="U153" s="20" t="n">
-        <v>-30.557</v>
-      </c>
-      <c r="V153" s="20" t="n">
-        <v>-35.365</v>
-      </c>
-      <c r="W153" s="20" t="n">
-        <v>-50.145</v>
-      </c>
-      <c r="X153" s="20" t="n">
-        <v>34.528</v>
+      <c r="A153" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C153" s="15">
+        <f>IF(OR(C152="",C139=""),"",IF(C139&lt;=0,"",IFERROR(C152/C139,"")))</f>
+        <v/>
+      </c>
+      <c r="D153" s="15">
+        <f>IF(OR(D152="",D139=""),"",IF(D139&lt;=0,"",IFERROR(D152/D139,"")))</f>
+        <v/>
+      </c>
+      <c r="E153" s="15">
+        <f>IF(OR(E152="",E139=""),"",IF(E139&lt;=0,"",IFERROR(E152/E139,"")))</f>
+        <v/>
+      </c>
+      <c r="F153" s="15">
+        <f>IF(OR(F152="",F139=""),"",IF(F139&lt;=0,"",IFERROR(F152/F139,"")))</f>
+        <v/>
+      </c>
+      <c r="G153" s="15">
+        <f>IF(OR(G152="",G139=""),"",IF(G139&lt;=0,"",IFERROR(G152/G139,"")))</f>
+        <v/>
+      </c>
+      <c r="H153" s="15">
+        <f>IF(OR(H152="",H139=""),"",IF(H139&lt;=0,"",IFERROR(H152/H139,"")))</f>
+        <v/>
+      </c>
+      <c r="I153" s="15">
+        <f>IF(OR(I152="",I139=""),"",IF(I139&lt;=0,"",IFERROR(I152/I139,"")))</f>
+        <v/>
+      </c>
+      <c r="J153" s="15">
+        <f>IF(OR(J152="",J139=""),"",IF(J139&lt;=0,"",IFERROR(J152/J139,"")))</f>
+        <v/>
+      </c>
+      <c r="K153" s="15">
+        <f>IF(OR(K152="",K139=""),"",IF(K139&lt;=0,"",IFERROR(K152/K139,"")))</f>
+        <v/>
+      </c>
+      <c r="L153" s="15">
+        <f>IF(OR(L152="",L139=""),"",IF(L139&lt;=0,"",IFERROR(L152/L139,"")))</f>
+        <v/>
+      </c>
+      <c r="M153" s="15">
+        <f>IF(OR(M152="",M139=""),"",IF(M139&lt;=0,"",IFERROR(M152/M139,"")))</f>
+        <v/>
+      </c>
+      <c r="N153" s="15">
+        <f>IF(OR(N152="",N139=""),"",IF(N139&lt;=0,"",IFERROR(N152/N139,"")))</f>
+        <v/>
+      </c>
+      <c r="V153" s="15">
+        <f>IF(OR(V152="",V139=""),"",IF(V139&lt;=0,"",IFERROR(V152/V139,"")))</f>
+        <v/>
+      </c>
+      <c r="W153" s="15">
+        <f>IF(OR(W152="",W139=""),"",IF(W139&lt;=0,"",IFERROR(W152/W139,"")))</f>
+        <v/>
+      </c>
+      <c r="X153" s="15">
+        <f>IF(OR(X152="",X139=""),"",IF(X139&lt;=0,"",IFERROR(X152/X139,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="18" t="inlineStr">
-        <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="D154" s="20" t="n">
-        <v>1.754</v>
-      </c>
-      <c r="F154" s="20" t="n">
-        <v>11.264</v>
-      </c>
-      <c r="H154" s="20" t="n">
-        <v>4.023</v>
-      </c>
-      <c r="J154" s="20" t="n">
-        <v>5.448</v>
-      </c>
-      <c r="L154" s="20" t="n">
-        <v>-101.247</v>
-      </c>
-      <c r="N154" s="20" t="n">
-        <v>-70.125</v>
-      </c>
-      <c r="S154" s="20" t="n">
-        <v>-6.379</v>
-      </c>
-      <c r="T154" s="20" t="n">
-        <v>-15.307</v>
-      </c>
-      <c r="U154" s="20" t="n">
-        <v>-47.863</v>
-      </c>
-      <c r="V154" s="20" t="n">
-        <v>11.264</v>
-      </c>
-      <c r="W154" s="20" t="n">
-        <v>5.448</v>
-      </c>
-      <c r="X154" s="20" t="n">
-        <v>-70.125</v>
+      <c r="A154" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G154" s="15">
+        <f>IF(OR(G152="",C152=""),"",IF(C152&lt;=0,"",IFERROR(G152/C152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H154" s="15">
+        <f>IF(OR(H152="",D152=""),"",IF(D152&lt;=0,"",IFERROR(H152/D152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I154" s="15">
+        <f>IF(OR(I152="",E152=""),"",IF(E152&lt;=0,"",IFERROR(I152/E152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J154" s="15">
+        <f>IF(OR(J152="",F152=""),"",IF(F152&lt;=0,"",IFERROR(J152/F152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K154" s="15">
+        <f>IF(OR(K152="",G152=""),"",IF(G152&lt;=0,"",IFERROR(K152/G152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L154" s="15">
+        <f>IF(OR(L152="",H152=""),"",IF(H152&lt;=0,"",IFERROR(L152/H152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M154" s="15">
+        <f>IF(OR(M152="",I152=""),"",IF(I152&lt;=0,"",IFERROR(M152/I152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N154" s="15">
+        <f>IF(OR(N152="",J152=""),"",IF(J152&lt;=0,"",IFERROR(N152/J152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V154" s="15">
+        <f>IF(OR(V152="",U152=""),"",IF(U152&lt;=0,"",IFERROR(V152/U152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W154" s="15">
+        <f>IF(OR(W152="",V152=""),"",IF(V152&lt;=0,"",IFERROR(W152/V152-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X154" s="15">
+        <f>IF(OR(X152="",W152=""),"",IF(W152&lt;=0,"",IFERROR(X152/W152-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
-        </is>
+          <t>기타 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="n">
+        <v>1.137</v>
       </c>
       <c r="D155" s="20" t="n">
-        <v>-9.808999999999999</v>
+        <v>1.118</v>
+      </c>
+      <c r="E155" s="20" t="n">
+        <v>1.14</v>
       </c>
       <c r="F155" s="20" t="n">
-        <v>-5.755</v>
+        <v>1.115</v>
+      </c>
+      <c r="G155" s="20" t="n">
+        <v>1.14</v>
       </c>
       <c r="H155" s="20" t="n">
-        <v>-0.782</v>
+        <v>0.048</v>
+      </c>
+      <c r="I155" s="20" t="n">
+        <v>0.059</v>
       </c>
       <c r="J155" s="20" t="n">
-        <v>-3.788</v>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="K155" s="20" t="n">
+        <v>0.061</v>
       </c>
       <c r="L155" s="20" t="n">
-        <v>8.529</v>
+        <v>0.061</v>
+      </c>
+      <c r="M155" s="20" t="n">
+        <v>0.054</v>
       </c>
       <c r="N155" s="20" t="n">
-        <v>21.848</v>
-      </c>
-      <c r="S155" s="20" t="n">
-        <v>1.266</v>
-      </c>
-      <c r="T155" s="20" t="n">
-        <v>-7.964</v>
-      </c>
-      <c r="U155" s="20" t="n">
-        <v>-6.249</v>
+        <v>0.044</v>
       </c>
       <c r="V155" s="20" t="n">
-        <v>-5.755</v>
+        <v>1.115</v>
       </c>
       <c r="W155" s="20" t="n">
-        <v>-3.788</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="X155" s="20" t="n">
-        <v>21.848</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="18" t="inlineStr">
-        <is>
-          <t>선급금 증감</t>
-        </is>
-      </c>
-      <c r="S156" s="20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T156" s="20" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="U156" s="20" t="n">
-        <v>0</v>
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C156" s="15">
+        <f>IF(OR(C155="",C141=""),"",IF(C141&lt;=0,"",IFERROR(C155/C141,"")))</f>
+        <v/>
+      </c>
+      <c r="D156" s="15">
+        <f>IF(OR(D155="",D141=""),"",IF(D141&lt;=0,"",IFERROR(D155/D141,"")))</f>
+        <v/>
+      </c>
+      <c r="E156" s="15">
+        <f>IF(OR(E155="",E141=""),"",IF(E141&lt;=0,"",IFERROR(E155/E141,"")))</f>
+        <v/>
+      </c>
+      <c r="F156" s="15">
+        <f>IF(OR(F155="",F141=""),"",IF(F141&lt;=0,"",IFERROR(F155/F141,"")))</f>
+        <v/>
+      </c>
+      <c r="G156" s="15">
+        <f>IF(OR(G155="",G141=""),"",IF(G141&lt;=0,"",IFERROR(G155/G141,"")))</f>
+        <v/>
+      </c>
+      <c r="H156" s="15">
+        <f>IF(OR(H155="",H141=""),"",IF(H141&lt;=0,"",IFERROR(H155/H141,"")))</f>
+        <v/>
+      </c>
+      <c r="I156" s="15">
+        <f>IF(OR(I155="",I141=""),"",IF(I141&lt;=0,"",IFERROR(I155/I141,"")))</f>
+        <v/>
+      </c>
+      <c r="J156" s="15">
+        <f>IF(OR(J155="",J141=""),"",IF(J141&lt;=0,"",IFERROR(J155/J141,"")))</f>
+        <v/>
+      </c>
+      <c r="K156" s="15">
+        <f>IF(OR(K155="",K141=""),"",IF(K141&lt;=0,"",IFERROR(K155/K141,"")))</f>
+        <v/>
+      </c>
+      <c r="L156" s="15">
+        <f>IF(OR(L155="",L141=""),"",IF(L141&lt;=0,"",IFERROR(L155/L141,"")))</f>
+        <v/>
+      </c>
+      <c r="M156" s="15">
+        <f>IF(OR(M155="",M141=""),"",IF(M141&lt;=0,"",IFERROR(M155/M141,"")))</f>
+        <v/>
+      </c>
+      <c r="N156" s="15">
+        <f>IF(OR(N155="",N141=""),"",IF(N141&lt;=0,"",IFERROR(N155/N141,"")))</f>
+        <v/>
+      </c>
+      <c r="V156" s="15">
+        <f>IF(OR(V155="",V141=""),"",IF(V141&lt;=0,"",IFERROR(V155/V141,"")))</f>
+        <v/>
+      </c>
+      <c r="W156" s="15">
+        <f>IF(OR(W155="",W141=""),"",IF(W141&lt;=0,"",IFERROR(W155/W141,"")))</f>
+        <v/>
+      </c>
+      <c r="X156" s="15">
+        <f>IF(OR(X155="",X141=""),"",IF(X141&lt;=0,"",IFERROR(X155/X141,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="18" t="inlineStr">
-        <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="D157" s="20" t="n">
-        <v>-6.408</v>
-      </c>
-      <c r="F157" s="20" t="n">
-        <v>-9.173999999999999</v>
-      </c>
-      <c r="H157" s="20" t="n">
-        <v>42.686</v>
-      </c>
-      <c r="J157" s="20" t="n">
-        <v>32.89</v>
-      </c>
-      <c r="L157" s="20" t="n">
-        <v>59.091</v>
-      </c>
-      <c r="N157" s="20" t="n">
-        <v>-15.531</v>
-      </c>
-      <c r="S157" s="20" t="n">
-        <v>20.973</v>
-      </c>
-      <c r="T157" s="20" t="n">
-        <v>-11.078</v>
-      </c>
-      <c r="U157" s="20" t="n">
-        <v>3.423</v>
-      </c>
-      <c r="V157" s="20" t="n">
-        <v>-9.173999999999999</v>
-      </c>
-      <c r="W157" s="20" t="n">
-        <v>32.89</v>
-      </c>
-      <c r="X157" s="20" t="n">
-        <v>-15.531</v>
+      <c r="A157" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G157" s="15">
+        <f>IF(OR(G155="",C155=""),"",IF(C155&lt;=0,"",IFERROR(G155/C155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H157" s="15">
+        <f>IF(OR(H155="",D155=""),"",IF(D155&lt;=0,"",IFERROR(H155/D155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I157" s="15">
+        <f>IF(OR(I155="",E155=""),"",IF(E155&lt;=0,"",IFERROR(I155/E155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J157" s="15">
+        <f>IF(OR(J155="",F155=""),"",IF(F155&lt;=0,"",IFERROR(J155/F155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K157" s="15">
+        <f>IF(OR(K155="",G155=""),"",IF(G155&lt;=0,"",IFERROR(K155/G155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L157" s="15">
+        <f>IF(OR(L155="",H155=""),"",IF(H155&lt;=0,"",IFERROR(L155/H155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M157" s="15">
+        <f>IF(OR(M155="",I155=""),"",IF(I155&lt;=0,"",IFERROR(M155/I155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N157" s="15">
+        <f>IF(OR(N155="",J155=""),"",IF(J155&lt;=0,"",IFERROR(N155/J155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V157" s="15">
+        <f>IF(OR(V155="",U155=""),"",IF(U155&lt;=0,"",IFERROR(V155/U155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W157" s="15">
+        <f>IF(OR(W155="",V155=""),"",IF(V155&lt;=0,"",IFERROR(W155/V155-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X157" s="15">
+        <f>IF(OR(X155="",W155=""),"",IF(W155&lt;=0,"",IFERROR(X155/W155-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
-        </is>
+          <t>합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="n">
+        <v>-20.517</v>
       </c>
       <c r="D158" s="20" t="n">
-        <v>-6.775</v>
+        <v>5.08</v>
+      </c>
+      <c r="E158" s="20" t="n">
+        <v>-20.146</v>
       </c>
       <c r="F158" s="20" t="n">
-        <v>9.632</v>
+        <v>4.308</v>
+      </c>
+      <c r="G158" s="20" t="n">
+        <v>8.606</v>
       </c>
       <c r="H158" s="20" t="n">
-        <v>-12.074</v>
+        <v>23.864</v>
+      </c>
+      <c r="I158" s="20" t="n">
+        <v>24.799</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>1.842</v>
+        <v>49.987</v>
+      </c>
+      <c r="K158" s="20" t="n">
+        <v>56.558</v>
       </c>
       <c r="L158" s="20" t="n">
-        <v>-6.535</v>
+        <v>48.366</v>
+      </c>
+      <c r="M158" s="20" t="n">
+        <v>44.309</v>
       </c>
       <c r="N158" s="20" t="n">
-        <v>-2.863</v>
-      </c>
-      <c r="S158" s="20" t="n">
-        <v>-0.959</v>
-      </c>
-      <c r="T158" s="20" t="n">
-        <v>16.891</v>
-      </c>
-      <c r="U158" s="20" t="n">
-        <v>3.363</v>
+        <v>112.769</v>
       </c>
       <c r="V158" s="20" t="n">
-        <v>9.632</v>
+        <v>4.308</v>
       </c>
       <c r="W158" s="20" t="n">
-        <v>1.842</v>
+        <v>49.987</v>
       </c>
       <c r="X158" s="20" t="n">
-        <v>-2.863</v>
+        <v>112.769</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="18" t="inlineStr">
-        <is>
-          <t>미지급비용 증감</t>
-        </is>
-      </c>
-      <c r="D159" s="20" t="n">
-        <v>-10.377</v>
-      </c>
-      <c r="F159" s="20" t="n">
-        <v>-10.623</v>
-      </c>
-      <c r="H159" s="20" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="J159" s="20" t="n">
-        <v>8.896000000000001</v>
-      </c>
-      <c r="L159" s="20" t="n">
-        <v>14.057</v>
-      </c>
-      <c r="N159" s="20" t="n">
-        <v>17.511</v>
-      </c>
-      <c r="S159" s="20" t="n">
-        <v>5.779</v>
-      </c>
-      <c r="T159" s="20" t="n">
-        <v>5.131</v>
-      </c>
-      <c r="U159" s="20" t="n">
-        <v>21.293</v>
-      </c>
-      <c r="V159" s="20" t="n">
-        <v>-10.623</v>
-      </c>
-      <c r="W159" s="20" t="n">
-        <v>8.896000000000001</v>
-      </c>
-      <c r="X159" s="20" t="n">
-        <v>17.511</v>
+      <c r="A159" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C159" s="15">
+        <f>IF(OR(C158="",C143=""),"",IF(C143&lt;=0,"",IFERROR(C158/C143,"")))</f>
+        <v/>
+      </c>
+      <c r="D159" s="15">
+        <f>IF(OR(D158="",D143=""),"",IF(D143&lt;=0,"",IFERROR(D158/D143,"")))</f>
+        <v/>
+      </c>
+      <c r="E159" s="15">
+        <f>IF(OR(E158="",E143=""),"",IF(E143&lt;=0,"",IFERROR(E158/E143,"")))</f>
+        <v/>
+      </c>
+      <c r="F159" s="15">
+        <f>IF(OR(F158="",F143=""),"",IF(F143&lt;=0,"",IFERROR(F158/F143,"")))</f>
+        <v/>
+      </c>
+      <c r="G159" s="15">
+        <f>IF(OR(G158="",G143=""),"",IF(G143&lt;=0,"",IFERROR(G158/G143,"")))</f>
+        <v/>
+      </c>
+      <c r="H159" s="15">
+        <f>IF(OR(H158="",H143=""),"",IF(H143&lt;=0,"",IFERROR(H158/H143,"")))</f>
+        <v/>
+      </c>
+      <c r="I159" s="15">
+        <f>IF(OR(I158="",I143=""),"",IF(I143&lt;=0,"",IFERROR(I158/I143,"")))</f>
+        <v/>
+      </c>
+      <c r="J159" s="15">
+        <f>IF(OR(J158="",J143=""),"",IF(J143&lt;=0,"",IFERROR(J158/J143,"")))</f>
+        <v/>
+      </c>
+      <c r="K159" s="15">
+        <f>IF(OR(K158="",K143=""),"",IF(K143&lt;=0,"",IFERROR(K158/K143,"")))</f>
+        <v/>
+      </c>
+      <c r="L159" s="15">
+        <f>IF(OR(L158="",L143=""),"",IF(L143&lt;=0,"",IFERROR(L158/L143,"")))</f>
+        <v/>
+      </c>
+      <c r="M159" s="15">
+        <f>IF(OR(M158="",M143=""),"",IF(M143&lt;=0,"",IFERROR(M158/M143,"")))</f>
+        <v/>
+      </c>
+      <c r="N159" s="15">
+        <f>IF(OR(N158="",N143=""),"",IF(N143&lt;=0,"",IFERROR(N158/N143,"")))</f>
+        <v/>
+      </c>
+      <c r="V159" s="15">
+        <f>IF(OR(V158="",V143=""),"",IF(V143&lt;=0,"",IFERROR(V158/V143,"")))</f>
+        <v/>
+      </c>
+      <c r="W159" s="15">
+        <f>IF(OR(W158="",W143=""),"",IF(W143&lt;=0,"",IFERROR(W158/W143,"")))</f>
+        <v/>
+      </c>
+      <c r="X159" s="15">
+        <f>IF(OR(X158="",X143=""),"",IF(X143&lt;=0,"",IFERROR(X158/X143,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="18" t="inlineStr">
-        <is>
-          <t>미지급법인세(외형표준과세) 증감</t>
-        </is>
-      </c>
-      <c r="D160" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F160" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" s="20" t="n">
-        <v>7.497</v>
-      </c>
-      <c r="J160" s="20" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="L160" s="20" t="n">
-        <v>-6.892</v>
-      </c>
-      <c r="N160" s="20" t="n">
-        <v>3.056</v>
-      </c>
-      <c r="V160" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" s="20" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="X160" s="20" t="n">
-        <v>3.056</v>
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G160" s="15">
+        <f>IF(OR(G158="",C158=""),"",IF(C158&lt;=0,"",IFERROR(G158/C158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H160" s="15">
+        <f>IF(OR(H158="",D158=""),"",IF(D158&lt;=0,"",IFERROR(H158/D158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I160" s="15">
+        <f>IF(OR(I158="",E158=""),"",IF(E158&lt;=0,"",IFERROR(I158/E158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J160" s="15">
+        <f>IF(OR(J158="",F158=""),"",IF(F158&lt;=0,"",IFERROR(J158/F158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K160" s="15">
+        <f>IF(OR(K158="",G158=""),"",IF(G158&lt;=0,"",IFERROR(K158/G158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L160" s="15">
+        <f>IF(OR(L158="",H158=""),"",IF(H158&lt;=0,"",IFERROR(L158/H158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M160" s="15">
+        <f>IF(OR(M158="",I158=""),"",IF(I158&lt;=0,"",IFERROR(M158/I158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N160" s="15">
+        <f>IF(OR(N158="",J158=""),"",IF(J158&lt;=0,"",IFERROR(N158/J158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V160" s="15">
+        <f>IF(OR(V158="",U158=""),"",IF(U158&lt;=0,"",IFERROR(V158/U158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W160" s="15">
+        <f>IF(OR(W158="",V158=""),"",IF(V158&lt;=0,"",IFERROR(W158/V158-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X160" s="15">
+        <f>IF(OR(X158="",W158=""),"",IF(W158&lt;=0,"",IFERROR(X158/W158-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>선수수익 증감</t>
-        </is>
+          <t>조정액 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="D161" s="20" t="n">
-        <v>40.994</v>
+        <v>0</v>
+      </c>
+      <c r="E161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="20" t="n">
-        <v>36.813</v>
+        <v>0</v>
+      </c>
+      <c r="G161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="H161" s="20" t="n">
-        <v>65.681</v>
+        <v>0</v>
+      </c>
+      <c r="I161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="J161" s="20" t="n">
-        <v>137.117</v>
+        <v>0</v>
+      </c>
+      <c r="K161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="L161" s="20" t="n">
-        <v>61.91</v>
+        <v>0</v>
+      </c>
+      <c r="M161" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="N161" s="20" t="n">
-        <v>184.848</v>
-      </c>
-      <c r="S161" s="20" t="n">
-        <v>9.128</v>
-      </c>
-      <c r="T161" s="20" t="n">
-        <v>87.982</v>
-      </c>
-      <c r="U161" s="20" t="n">
-        <v>43.755</v>
+        <v>0</v>
       </c>
       <c r="V161" s="20" t="n">
-        <v>36.813</v>
+        <v>0</v>
       </c>
       <c r="W161" s="20" t="n">
-        <v>137.117</v>
+        <v>0</v>
       </c>
       <c r="X161" s="20" t="n">
-        <v>184.848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
-        </is>
-      </c>
-      <c r="F162" s="20" t="n">
-        <v>2.759</v>
-      </c>
-      <c r="J162" s="20" t="n">
-        <v>2.909</v>
-      </c>
-      <c r="N162" s="20" t="n">
-        <v>-3.321</v>
-      </c>
-      <c r="S162" s="20" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="T162" s="20" t="n">
-        <v>-0.143</v>
-      </c>
-      <c r="U162" s="20" t="n">
-        <v>1.668</v>
-      </c>
-      <c r="V162" s="20" t="n">
-        <v>2.759</v>
-      </c>
-      <c r="W162" s="20" t="n">
-        <v>2.909</v>
-      </c>
-      <c r="X162" s="20" t="n">
-        <v>-3.321</v>
+          <t>EntityTotalMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="G162" s="20" t="n">
+        <v>8.606</v>
+      </c>
+      <c r="K162" s="20" t="n">
+        <v>56.558</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="18" t="inlineStr">
-        <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="D163" s="20" t="n">
-        <v>9.917</v>
-      </c>
-      <c r="F163" s="20" t="n">
-        <v>20.218</v>
-      </c>
-      <c r="H163" s="20" t="n">
-        <v>-1.878</v>
-      </c>
-      <c r="J163" s="20" t="n">
-        <v>17.536</v>
-      </c>
-      <c r="L163" s="20" t="n">
-        <v>-21.713</v>
-      </c>
-      <c r="N163" s="20" t="n">
-        <v>-6.527</v>
-      </c>
-      <c r="S163" s="20" t="n">
-        <v>-1.337</v>
-      </c>
-      <c r="T163" s="20" t="n">
-        <v>9.618</v>
-      </c>
-      <c r="U163" s="20" t="n">
-        <v>-13.731</v>
-      </c>
-      <c r="V163" s="20" t="n">
-        <v>20.218</v>
-      </c>
-      <c r="W163" s="20" t="n">
-        <v>17.536</v>
-      </c>
-      <c r="X163" s="20" t="n">
-        <v>-6.527</v>
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>부문 이익</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="n">
+        <v>-20.517</v>
+      </c>
+      <c r="D163" s="12" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>-20.146</v>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>4.308</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>8.606</v>
+      </c>
+      <c r="H163" s="12" t="n">
+        <v>23.864</v>
+      </c>
+      <c r="I163" s="12" t="n">
+        <v>24.799</v>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>49.987</v>
+      </c>
+      <c r="V163" s="12" t="n">
+        <v>4.308</v>
+      </c>
+      <c r="W163" s="12" t="n">
+        <v>49.987</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="18" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="D164" s="20" t="n">
-        <v>-0.5649999999999999</v>
-      </c>
-      <c r="F164" s="20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H164" s="20" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J164" s="20" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="L164" s="20" t="n">
-        <v>4.225</v>
-      </c>
-      <c r="N164" s="20" t="n">
-        <v>-1.449</v>
-      </c>
-      <c r="S164" s="20" t="n">
-        <v>1.607</v>
-      </c>
-      <c r="T164" s="20" t="n">
-        <v>-2.757</v>
-      </c>
-      <c r="U164" s="20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V164" s="20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W164" s="20" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="X164" s="20" t="n">
-        <v>-1.449</v>
+      <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C164" s="15">
+        <f>IF(OR(C163="",C128=""),"",IF(C128&lt;=0,"",IFERROR(C163/C128,"")))</f>
+        <v/>
+      </c>
+      <c r="D164" s="15">
+        <f>IF(OR(D163="",D128=""),"",IF(D128&lt;=0,"",IFERROR(D163/D128,"")))</f>
+        <v/>
+      </c>
+      <c r="E164" s="15">
+        <f>IF(OR(E163="",E128=""),"",IF(E128&lt;=0,"",IFERROR(E163/E128,"")))</f>
+        <v/>
+      </c>
+      <c r="F164" s="15">
+        <f>IF(OR(F163="",F128=""),"",IF(F128&lt;=0,"",IFERROR(F163/F128,"")))</f>
+        <v/>
+      </c>
+      <c r="G164" s="15">
+        <f>IF(OR(G163="",G128=""),"",IF(G128&lt;=0,"",IFERROR(G163/G128,"")))</f>
+        <v/>
+      </c>
+      <c r="H164" s="15">
+        <f>IF(OR(H163="",H128=""),"",IF(H128&lt;=0,"",IFERROR(H163/H128,"")))</f>
+        <v/>
+      </c>
+      <c r="I164" s="15">
+        <f>IF(OR(I163="",I128=""),"",IF(I128&lt;=0,"",IFERROR(I163/I128,"")))</f>
+        <v/>
+      </c>
+      <c r="J164" s="15">
+        <f>IF(OR(J163="",J128=""),"",IF(J128&lt;=0,"",IFERROR(J163/J128,"")))</f>
+        <v/>
+      </c>
+      <c r="V164" s="15">
+        <f>IF(OR(V163="",V128=""),"",IF(V128&lt;=0,"",IFERROR(V163/V128,"")))</f>
+        <v/>
+      </c>
+      <c r="W164" s="15">
+        <f>IF(OR(W163="",W128=""),"",IF(W128&lt;=0,"",IFERROR(W163/W128,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="18" t="inlineStr">
-        <is>
-          <t>소계</t>
-        </is>
-      </c>
-      <c r="D165" s="20" t="n">
-        <v>-7.808</v>
-      </c>
-      <c r="F165" s="20" t="n">
-        <v>3.063</v>
-      </c>
-      <c r="H165" s="20" t="n">
-        <v>134.246</v>
-      </c>
-      <c r="J165" s="20" t="n">
-        <v>290.904</v>
-      </c>
-      <c r="L165" s="20" t="n">
-        <v>132.68</v>
-      </c>
-      <c r="N165" s="20" t="n">
-        <v>449.673</v>
-      </c>
-      <c r="S165" s="20" t="n">
-        <v>-96.83799999999999</v>
-      </c>
-      <c r="T165" s="20" t="n">
-        <v>111.533</v>
-      </c>
-      <c r="U165" s="20" t="n">
-        <v>-66.726</v>
-      </c>
-      <c r="V165" s="20" t="n">
-        <v>3.063</v>
-      </c>
-      <c r="W165" s="20" t="n">
-        <v>290.904</v>
-      </c>
-      <c r="X165" s="20" t="n">
-        <v>449.673</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="18" t="inlineStr">
-        <is>
-          <t>이자·배당금 수취</t>
-        </is>
-      </c>
-      <c r="D166" s="20" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="F166" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H166" s="20" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="J166" s="20" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="L166" s="20" t="n">
-        <v>1.706</v>
-      </c>
-      <c r="N166" s="20" t="n">
-        <v>5.036</v>
-      </c>
-      <c r="S166" s="20" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="T166" s="20" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="U166" s="20" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="V166" s="20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="W166" s="20" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="X166" s="20" t="n">
-        <v>5.036</v>
+      <c r="A165" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G165" s="15">
+        <f>IF(OR(G163="",C163=""),"",IF(C163&lt;=0,"",IFERROR(G163/C163-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H165" s="15">
+        <f>IF(OR(H163="",D163=""),"",IF(D163&lt;=0,"",IFERROR(H163/D163-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I165" s="15">
+        <f>IF(OR(I163="",E163=""),"",IF(E163&lt;=0,"",IFERROR(I163/E163-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J165" s="15">
+        <f>IF(OR(J163="",F163=""),"",IF(F163&lt;=0,"",IFERROR(J163/F163-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V165" s="15">
+        <f>IF(OR(V163="",U163=""),"",IF(U163&lt;=0,"",IFERROR(V163/U163-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W165" s="15">
+        <f>IF(OR(W163="",V163=""),"",IF(V163&lt;=0,"",IFERROR(W163/V163-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="18" t="inlineStr">
-        <is>
-          <t>업무수탁료 수취</t>
-        </is>
-      </c>
-      <c r="S167" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U167" s="20" t="n">
-        <v>0</v>
-      </c>
+      <c r="A167" s="16" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B167" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="n"/>
+      <c r="D167" s="16" t="n"/>
+      <c r="E167" s="16" t="n"/>
+      <c r="F167" s="16" t="n"/>
+      <c r="G167" s="16" t="n"/>
+      <c r="H167" s="16" t="n"/>
+      <c r="I167" s="16" t="n"/>
+      <c r="J167" s="16" t="n"/>
+      <c r="K167" s="16" t="n"/>
+      <c r="L167" s="16" t="n"/>
+      <c r="M167" s="16" t="n"/>
+      <c r="N167" s="16" t="n"/>
+      <c r="O167" s="16" t="n"/>
+      <c r="P167" s="16" t="n"/>
+      <c r="Q167" s="16" t="n"/>
+      <c r="R167" s="16" t="n"/>
+      <c r="S167" s="16" t="n"/>
+      <c r="T167" s="16" t="n"/>
+      <c r="U167" s="16" t="n"/>
+      <c r="V167" s="16" t="n"/>
+      <c r="W167" s="16" t="n"/>
+      <c r="X167" s="16" t="n"/>
+      <c r="Y167" s="16" t="n"/>
+      <c r="Z167" s="16" t="n"/>
+      <c r="AA167" s="16" t="n"/>
+      <c r="AB167" s="16" t="n"/>
+      <c r="AC167" s="16" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="18" t="inlineStr">
-        <is>
-          <t>보조금 수취</t>
-        </is>
-      </c>
-      <c r="D168" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F168" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H168" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W168" s="20" t="n">
-        <v>0</v>
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>2024.1Q</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="L168" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="M168" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="O168" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P168" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q168" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R168" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S168" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T168" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U168" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V168" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W168" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X168" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y168" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z168" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA168" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB168" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC168" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="18" t="inlineStr">
-        <is>
-          <t>포상금 수취</t>
-        </is>
-      </c>
-      <c r="D169" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T169" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U169" s="20" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V169" s="20" t="n">
-        <v>0</v>
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="n">
+        <v>-16.988</v>
+      </c>
+      <c r="F169" s="12" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H169" s="12" t="n">
+        <v>17.439</v>
+      </c>
+      <c r="J169" s="12" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="L169" s="12" t="n">
+        <v>103.292</v>
+      </c>
+      <c r="N169" s="12" t="n">
+        <v>262.775</v>
+      </c>
+      <c r="S169" s="12" t="n">
+        <v>-95.666</v>
+      </c>
+      <c r="T169" s="12" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="U169" s="12" t="n">
+        <v>-72.468</v>
+      </c>
+      <c r="V169" s="12" t="n">
+        <v>-34</v>
+      </c>
+      <c r="W169" s="12" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X169" s="12" t="n">
+        <v>262.775</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="D170" s="20" t="n">
-        <v>-0.877</v>
+        <v>6.718</v>
       </c>
       <c r="F170" s="20" t="n">
-        <v>-1.714</v>
+        <v>13.64</v>
       </c>
       <c r="H170" s="20" t="n">
-        <v>-0.799</v>
+        <v>7.239</v>
       </c>
       <c r="J170" s="20" t="n">
-        <v>-1.654</v>
+        <v>15.884</v>
       </c>
       <c r="L170" s="20" t="n">
-        <v>-0.676</v>
+        <v>28.413</v>
       </c>
       <c r="N170" s="20" t="n">
-        <v>-1.31</v>
+        <v>28.641</v>
       </c>
       <c r="S170" s="20" t="n">
-        <v>-0.5629999999999999</v>
+        <v>1.594</v>
       </c>
       <c r="T170" s="20" t="n">
-        <v>0</v>
+        <v>3.997</v>
       </c>
       <c r="U170" s="20" t="n">
-        <v>0</v>
+        <v>21.665</v>
       </c>
       <c r="V170" s="20" t="n">
-        <v>-1.714</v>
+        <v>13.64</v>
       </c>
       <c r="W170" s="20" t="n">
-        <v>-1.654</v>
+        <v>15.884</v>
       </c>
       <c r="X170" s="20" t="n">
-        <v>-1.31</v>
+        <v>28.641</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
-      </c>
-      <c r="D171" s="20" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="F171" s="20" t="n">
-        <v>-0.29</v>
+          <t>상여충당금 증감</t>
+        </is>
       </c>
       <c r="H171" s="20" t="n">
-        <v>-0.485</v>
-      </c>
-      <c r="J171" s="20" t="n">
-        <v>-0.485</v>
+        <v>0</v>
       </c>
       <c r="L171" s="20" t="n">
-        <v>-21.342</v>
-      </c>
-      <c r="N171" s="20" t="n">
-        <v>-40.216</v>
-      </c>
-      <c r="S171" s="20" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="T171" s="20" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="U171" s="20" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="V171" s="20" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="W171" s="20" t="n">
-        <v>-0.485</v>
-      </c>
-      <c r="X171" s="20" t="n">
-        <v>-40.216</v>
+        <v>7.326</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D172" s="12" t="n">
-        <v>-8.933</v>
-      </c>
-      <c r="F172" s="12" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="H172" s="12" t="n">
-        <v>133.474</v>
-      </c>
-      <c r="J172" s="12" t="n">
-        <v>290.705</v>
-      </c>
-      <c r="L172" s="12" t="n">
-        <v>112.367</v>
-      </c>
-      <c r="N172" s="12" t="n">
-        <v>413.183</v>
-      </c>
-      <c r="S172" s="12" t="n">
-        <v>-97.687</v>
-      </c>
-      <c r="T172" s="12" t="n">
-        <v>114.249</v>
-      </c>
-      <c r="U172" s="12" t="n">
-        <v>-66.91800000000001</v>
-      </c>
-      <c r="V172" s="12" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="W172" s="12" t="n">
-        <v>290.705</v>
-      </c>
-      <c r="X172" s="12" t="n">
-        <v>413.183</v>
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F172" s="20" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H172" s="20" t="n">
+        <v>-0.513</v>
+      </c>
+      <c r="J172" s="20" t="n">
+        <v>-1.942</v>
+      </c>
+      <c r="L172" s="20" t="n">
+        <v>-1.706</v>
+      </c>
+      <c r="N172" s="20" t="n">
+        <v>-3.609</v>
+      </c>
+      <c r="S172" s="20" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="T172" s="20" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="U172" s="20" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="V172" s="20" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W172" s="20" t="n">
+        <v>-1.942</v>
+      </c>
+      <c r="X172" s="20" t="n">
+        <v>-3.609</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="D173" s="20" t="n">
-        <v>-44.906</v>
+        <v>-0.04</v>
       </c>
       <c r="F173" s="20" t="n">
-        <v>-47.532</v>
+        <v>-0.04</v>
       </c>
       <c r="H173" s="20" t="n">
-        <v>-3.573</v>
+        <v>0</v>
       </c>
       <c r="J173" s="20" t="n">
-        <v>-18.939</v>
-      </c>
-      <c r="L173" s="20" t="n">
-        <v>-2.626</v>
-      </c>
-      <c r="N173" s="20" t="n">
-        <v>-4.413</v>
-      </c>
-      <c r="S173" s="20" t="n">
-        <v>-0.753</v>
-      </c>
-      <c r="T173" s="20" t="n">
-        <v>-18.462</v>
+        <v>0</v>
       </c>
       <c r="U173" s="20" t="n">
-        <v>-20.958</v>
+        <v>0</v>
       </c>
       <c r="V173" s="20" t="n">
-        <v>-47.532</v>
+        <v>-0.04</v>
       </c>
       <c r="W173" s="20" t="n">
-        <v>-18.939</v>
-      </c>
-      <c r="X173" s="20" t="n">
-        <v>-4.413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="F174" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T174" s="20" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U174" s="20" t="n">
-        <v>-10</v>
-      </c>
-      <c r="V174" s="20" t="n">
-        <v>0</v>
+          <t>유가증권 이자</t>
+        </is>
+      </c>
+      <c r="J174" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" s="20" t="n">
+        <v>-1.426</v>
+      </c>
+      <c r="W174" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X174" s="20" t="n">
+        <v>-1.426</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="D175" s="20" t="n">
-        <v>-7.53</v>
+          <t>외환차손익</t>
+        </is>
       </c>
       <c r="F175" s="20" t="n">
-        <v>-7.53</v>
-      </c>
-      <c r="H175" s="20" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="J175" s="20" t="n">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="N175" s="20" t="n">
+        <v>-0.006</v>
       </c>
       <c r="U175" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V175" s="20" t="n">
-        <v>-7.53</v>
+        <v>0.004</v>
       </c>
       <c r="W175" s="20" t="n">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="X175" s="20" t="n">
+        <v>-0.006</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>임차보증금 납입</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="D176" s="20" t="n">
-        <v>0</v>
+        <v>0.785</v>
       </c>
       <c r="F176" s="20" t="n">
-        <v>0</v>
+        <v>1.619</v>
       </c>
       <c r="H176" s="20" t="n">
-        <v>-0.72</v>
+        <v>0.8</v>
       </c>
       <c r="J176" s="20" t="n">
-        <v>-7.943</v>
+        <v>1.667</v>
       </c>
       <c r="L176" s="20" t="n">
-        <v>-119.172</v>
+        <v>0.68</v>
       </c>
       <c r="N176" s="20" t="n">
-        <v>-119.684</v>
+        <v>1.325</v>
       </c>
       <c r="S176" s="20" t="n">
-        <v>0</v>
+        <v>0.576</v>
       </c>
       <c r="T176" s="20" t="n">
-        <v>-11.25</v>
+        <v>0</v>
       </c>
       <c r="U176" s="20" t="n">
-        <v>-61.773</v>
+        <v>0</v>
       </c>
       <c r="V176" s="20" t="n">
-        <v>0</v>
+        <v>1.619</v>
       </c>
       <c r="W176" s="20" t="n">
-        <v>-7.943</v>
+        <v>1.667</v>
       </c>
       <c r="X176" s="20" t="n">
-        <v>-119.684</v>
+        <v>1.325</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>임차보증금 반환</t>
-        </is>
-      </c>
-      <c r="S177" s="20" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="T177" s="20" t="n">
-        <v>0.057</v>
+          <t>투자유가증권 평가손익</t>
+        </is>
+      </c>
+      <c r="D177" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="U177" s="20" t="n">
+        <v>4.999</v>
+      </c>
+      <c r="V177" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>임차보증금 회수</t>
+          <t>주식교부비</t>
         </is>
       </c>
       <c r="D178" s="20" t="n">
-        <v>26.178</v>
+        <v>0</v>
       </c>
       <c r="F178" s="20" t="n">
-        <v>26.178</v>
+        <v>0</v>
       </c>
       <c r="H178" s="20" t="n">
-        <v>0</v>
+        <v>14.011</v>
       </c>
       <c r="J178" s="20" t="n">
-        <v>0</v>
+        <v>14.011</v>
+      </c>
+      <c r="L178" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" s="20" t="n">
+        <v>4.353</v>
       </c>
       <c r="U178" s="20" t="n">
         <v>0</v>
       </c>
       <c r="V178" s="20" t="n">
-        <v>26.178</v>
+        <v>0</v>
       </c>
       <c r="W178" s="20" t="n">
+        <v>14.011</v>
+      </c>
+      <c r="X178" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="18" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="D179" s="20" t="n">
+        <v>-17.01</v>
       </c>
       <c r="F179" s="20" t="n">
-        <v>-3.7</v>
+        <v>-35.365</v>
+      </c>
+      <c r="H179" s="20" t="n">
+        <v>-11.636</v>
       </c>
       <c r="J179" s="20" t="n">
-        <v>0</v>
+        <v>-50.145</v>
+      </c>
+      <c r="L179" s="20" t="n">
+        <v>-16.752</v>
+      </c>
+      <c r="N179" s="20" t="n">
+        <v>34.528</v>
+      </c>
+      <c r="S179" s="20" t="n">
+        <v>-35.703</v>
       </c>
       <c r="T179" s="20" t="n">
-        <v>0</v>
+        <v>10.947</v>
       </c>
       <c r="U179" s="20" t="n">
-        <v>-14.4</v>
+        <v>-30.557</v>
       </c>
       <c r="V179" s="20" t="n">
-        <v>-3.7</v>
+        <v>-35.365</v>
       </c>
       <c r="W179" s="20" t="n">
-        <v>0</v>
+        <v>-50.145</v>
+      </c>
+      <c r="X179" s="20" t="n">
+        <v>34.528</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D180" s="12" t="n">
-        <v>-26.257</v>
-      </c>
-      <c r="F180" s="12" t="n">
-        <v>-32.583</v>
-      </c>
-      <c r="H180" s="12" t="n">
-        <v>-4.293</v>
-      </c>
-      <c r="J180" s="12" t="n">
-        <v>-26.883</v>
-      </c>
-      <c r="L180" s="12" t="n">
-        <v>-121.799</v>
-      </c>
-      <c r="N180" s="12" t="n">
-        <v>-124.098</v>
-      </c>
-      <c r="S180" s="12" t="n">
-        <v>-0.6909999999999999</v>
-      </c>
-      <c r="T180" s="12" t="n">
-        <v>-34.654</v>
-      </c>
-      <c r="U180" s="12" t="n">
-        <v>-107.132</v>
-      </c>
-      <c r="V180" s="12" t="n">
-        <v>-32.583</v>
-      </c>
-      <c r="W180" s="12" t="n">
-        <v>-26.883</v>
-      </c>
-      <c r="X180" s="12" t="n">
-        <v>-124.098</v>
+      <c r="A180" s="18" t="inlineStr">
+        <is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="D180" s="20" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="F180" s="20" t="n">
+        <v>11.264</v>
+      </c>
+      <c r="H180" s="20" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="J180" s="20" t="n">
+        <v>5.448</v>
+      </c>
+      <c r="L180" s="20" t="n">
+        <v>-101.247</v>
+      </c>
+      <c r="N180" s="20" t="n">
+        <v>-70.125</v>
+      </c>
+      <c r="S180" s="20" t="n">
+        <v>-6.379</v>
+      </c>
+      <c r="T180" s="20" t="n">
+        <v>-15.307</v>
+      </c>
+      <c r="U180" s="20" t="n">
+        <v>-47.863</v>
+      </c>
+      <c r="V180" s="20" t="n">
+        <v>11.264</v>
+      </c>
+      <c r="W180" s="20" t="n">
+        <v>5.448</v>
+      </c>
+      <c r="X180" s="20" t="n">
+        <v>-70.125</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
+          <t>선급비용 증감</t>
+        </is>
+      </c>
+      <c r="D181" s="20" t="n">
+        <v>-9.808999999999999</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0</v>
+        <v>-5.755</v>
+      </c>
+      <c r="H181" s="20" t="n">
+        <v>-0.782</v>
       </c>
       <c r="J181" s="20" t="n">
-        <v>50</v>
+        <v>-3.788</v>
+      </c>
+      <c r="L181" s="20" t="n">
+        <v>8.529</v>
       </c>
       <c r="N181" s="20" t="n">
-        <v>0</v>
+        <v>21.848</v>
+      </c>
+      <c r="S181" s="20" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="T181" s="20" t="n">
+        <v>-7.964</v>
+      </c>
+      <c r="U181" s="20" t="n">
+        <v>-6.249</v>
       </c>
       <c r="V181" s="20" t="n">
-        <v>0</v>
+        <v>-5.755</v>
       </c>
       <c r="W181" s="20" t="n">
-        <v>50</v>
+        <v>-3.788</v>
       </c>
       <c r="X181" s="20" t="n">
-        <v>0</v>
+        <v>21.848</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
-        </is>
-      </c>
-      <c r="F182" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J182" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="N182" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W182" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="X182" s="20" t="n">
+          <t>선급금 증감</t>
+        </is>
+      </c>
+      <c r="S182" s="20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T182" s="20" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U182" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="D183" s="20" t="n">
-        <v>109</v>
+        <v>-6.408</v>
       </c>
       <c r="F183" s="20" t="n">
-        <v>109</v>
+        <v>-9.173999999999999</v>
       </c>
       <c r="H183" s="20" t="n">
-        <v>0</v>
+        <v>42.686</v>
       </c>
       <c r="J183" s="20" t="n">
-        <v>0</v>
+        <v>32.89</v>
+      </c>
+      <c r="L183" s="20" t="n">
+        <v>59.091</v>
+      </c>
+      <c r="N183" s="20" t="n">
+        <v>-15.531</v>
+      </c>
+      <c r="S183" s="20" t="n">
+        <v>20.973</v>
+      </c>
+      <c r="T183" s="20" t="n">
+        <v>-11.078</v>
       </c>
       <c r="U183" s="20" t="n">
-        <v>0</v>
+        <v>3.423</v>
       </c>
       <c r="V183" s="20" t="n">
-        <v>109</v>
+        <v>-9.173999999999999</v>
       </c>
       <c r="W183" s="20" t="n">
-        <v>0</v>
+        <v>32.89</v>
+      </c>
+      <c r="X183" s="20" t="n">
+        <v>-15.531</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="D184" s="20" t="n">
-        <v>-9.08</v>
+        <v>-6.775</v>
       </c>
       <c r="F184" s="20" t="n">
-        <v>-19.976</v>
+        <v>9.632</v>
       </c>
       <c r="H184" s="20" t="n">
-        <v>-10.896</v>
+        <v>-12.074</v>
       </c>
       <c r="J184" s="20" t="n">
-        <v>-21.792</v>
+        <v>1.842</v>
       </c>
       <c r="L184" s="20" t="n">
-        <v>-10.896</v>
+        <v>-6.535</v>
       </c>
       <c r="N184" s="20" t="n">
-        <v>-21.792</v>
+        <v>-2.863</v>
       </c>
       <c r="S184" s="20" t="n">
-        <v>-64.82899999999999</v>
+        <v>-0.959</v>
       </c>
       <c r="T184" s="20" t="n">
-        <v>0</v>
+        <v>16.891</v>
       </c>
       <c r="U184" s="20" t="n">
-        <v>0</v>
+        <v>3.363</v>
       </c>
       <c r="V184" s="20" t="n">
-        <v>-19.976</v>
+        <v>9.632</v>
       </c>
       <c r="W184" s="20" t="n">
-        <v>-21.792</v>
+        <v>1.842</v>
       </c>
       <c r="X184" s="20" t="n">
-        <v>-21.792</v>
+        <v>-2.863</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>주식 발행</t>
+          <t>미지급비용 증감</t>
         </is>
       </c>
       <c r="D185" s="20" t="n">
-        <v>0</v>
+        <v>-10.377</v>
       </c>
       <c r="F185" s="20" t="n">
-        <v>0</v>
+        <v>-10.623</v>
       </c>
       <c r="H185" s="20" t="n">
-        <v>767.208</v>
+        <v>2.401</v>
       </c>
       <c r="J185" s="20" t="n">
-        <v>767.208</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="L185" s="20" t="n">
-        <v>0</v>
+        <v>14.057</v>
       </c>
       <c r="N185" s="20" t="n">
-        <v>0</v>
+        <v>17.511</v>
+      </c>
+      <c r="S185" s="20" t="n">
+        <v>5.779</v>
+      </c>
+      <c r="T185" s="20" t="n">
+        <v>5.131</v>
+      </c>
+      <c r="U185" s="20" t="n">
+        <v>21.293</v>
       </c>
       <c r="V185" s="20" t="n">
-        <v>0</v>
+        <v>-10.623</v>
       </c>
       <c r="W185" s="20" t="n">
-        <v>767.208</v>
+        <v>8.896000000000001</v>
       </c>
       <c r="X185" s="20" t="n">
-        <v>0</v>
+        <v>17.511</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>미지급법인세(외형표준과세) 증감</t>
         </is>
       </c>
       <c r="D186" s="20" t="n">
@@ -10518,193 +11160,1074 @@
         <v>0</v>
       </c>
       <c r="H186" s="20" t="n">
-        <v>-0.011</v>
+        <v>7.497</v>
       </c>
       <c r="J186" s="20" t="n">
-        <v>-0.011</v>
+        <v>15.54</v>
       </c>
       <c r="L186" s="20" t="n">
-        <v>0</v>
+        <v>-6.892</v>
       </c>
       <c r="N186" s="20" t="n">
-        <v>0</v>
+        <v>3.056</v>
       </c>
       <c r="V186" s="20" t="n">
         <v>0</v>
       </c>
       <c r="W186" s="20" t="n">
-        <v>-0.011</v>
+        <v>15.54</v>
       </c>
       <c r="X186" s="20" t="n">
-        <v>0</v>
+        <v>3.056</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>자기주식 처분</t>
+          <t>선수수익 증감</t>
         </is>
       </c>
       <c r="D187" s="20" t="n">
-        <v>0</v>
+        <v>40.994</v>
       </c>
       <c r="F187" s="20" t="n">
-        <v>0</v>
+        <v>36.813</v>
       </c>
       <c r="H187" s="20" t="n">
-        <v>0</v>
+        <v>65.681</v>
       </c>
       <c r="J187" s="20" t="n">
-        <v>7.7</v>
+        <v>137.117</v>
       </c>
       <c r="L187" s="20" t="n">
-        <v>4.7</v>
+        <v>61.91</v>
       </c>
       <c r="N187" s="20" t="n">
-        <v>4.7</v>
+        <v>184.848</v>
       </c>
       <c r="S187" s="20" t="n">
-        <v>50.15</v>
+        <v>9.128</v>
       </c>
       <c r="T187" s="20" t="n">
-        <v>323.787</v>
+        <v>87.982</v>
       </c>
       <c r="U187" s="20" t="n">
-        <v>14.9</v>
+        <v>43.755</v>
       </c>
       <c r="V187" s="20" t="n">
-        <v>0</v>
+        <v>36.813</v>
       </c>
       <c r="W187" s="20" t="n">
-        <v>7.7</v>
+        <v>137.117</v>
       </c>
       <c r="X187" s="20" t="n">
-        <v>4.7</v>
+        <v>184.848</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D188" s="12" t="n">
-        <v>99.92</v>
-      </c>
-      <c r="F188" s="12" t="n">
-        <v>89.024</v>
-      </c>
-      <c r="H188" s="12" t="n">
-        <v>756.3</v>
-      </c>
-      <c r="J188" s="12" t="n">
-        <v>753.104</v>
-      </c>
-      <c r="L188" s="12" t="n">
-        <v>-6.196</v>
-      </c>
-      <c r="N188" s="12" t="n">
-        <v>-17.092</v>
-      </c>
-      <c r="S188" s="12" t="n">
-        <v>-14.679</v>
-      </c>
-      <c r="T188" s="12" t="n">
-        <v>323.787</v>
-      </c>
-      <c r="U188" s="12" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V188" s="12" t="n">
-        <v>89.024</v>
-      </c>
-      <c r="W188" s="12" t="n">
-        <v>753.104</v>
-      </c>
-      <c r="X188" s="12" t="n">
-        <v>-17.092</v>
+      <c r="A188" s="18" t="inlineStr">
+        <is>
+          <t>예수금 증감</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="J188" s="20" t="n">
+        <v>2.909</v>
+      </c>
+      <c r="N188" s="20" t="n">
+        <v>-3.321</v>
+      </c>
+      <c r="S188" s="20" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="T188" s="20" t="n">
+        <v>-0.143</v>
+      </c>
+      <c r="U188" s="20" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="V188" s="20" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="W188" s="20" t="n">
+        <v>2.909</v>
+      </c>
+      <c r="X188" s="20" t="n">
+        <v>-3.321</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="D189" s="20" t="n">
-        <v>0</v>
+        <v>9.917</v>
       </c>
       <c r="F189" s="20" t="n">
-        <v>-0.004</v>
+        <v>20.218</v>
       </c>
       <c r="H189" s="20" t="n">
-        <v>0.003</v>
+        <v>-1.878</v>
       </c>
       <c r="J189" s="20" t="n">
-        <v>0.001</v>
+        <v>17.536</v>
       </c>
       <c r="L189" s="20" t="n">
-        <v>0.006</v>
+        <v>-21.713</v>
       </c>
       <c r="N189" s="20" t="n">
-        <v>0.006</v>
+        <v>-6.527</v>
+      </c>
+      <c r="S189" s="20" t="n">
+        <v>-1.337</v>
       </c>
       <c r="T189" s="20" t="n">
-        <v>0</v>
+        <v>9.618</v>
       </c>
       <c r="U189" s="20" t="n">
-        <v>0</v>
+        <v>-13.731</v>
       </c>
       <c r="V189" s="20" t="n">
-        <v>-0.004</v>
+        <v>20.218</v>
       </c>
       <c r="W189" s="20" t="n">
-        <v>0.001</v>
+        <v>17.536</v>
       </c>
       <c r="X189" s="20" t="n">
-        <v>0.006</v>
+        <v>-6.527</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D190" s="20" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="F190" s="20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H190" s="20" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J190" s="20" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L190" s="20" t="n">
+        <v>4.225</v>
+      </c>
+      <c r="N190" s="20" t="n">
+        <v>-1.449</v>
+      </c>
+      <c r="S190" s="20" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="T190" s="20" t="n">
+        <v>-2.757</v>
+      </c>
+      <c r="U190" s="20" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V190" s="20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W190" s="20" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="X190" s="20" t="n">
+        <v>-1.449</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="D191" s="20" t="n">
+        <v>-7.808</v>
+      </c>
+      <c r="F191" s="20" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="H191" s="20" t="n">
+        <v>134.246</v>
+      </c>
+      <c r="J191" s="20" t="n">
+        <v>290.904</v>
+      </c>
+      <c r="L191" s="20" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="N191" s="20" t="n">
+        <v>449.673</v>
+      </c>
+      <c r="S191" s="20" t="n">
+        <v>-96.83799999999999</v>
+      </c>
+      <c r="T191" s="20" t="n">
+        <v>111.533</v>
+      </c>
+      <c r="U191" s="20" t="n">
+        <v>-66.726</v>
+      </c>
+      <c r="V191" s="20" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="W191" s="20" t="n">
+        <v>290.904</v>
+      </c>
+      <c r="X191" s="20" t="n">
+        <v>449.673</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="D192" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F192" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H192" s="20" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="J192" s="20" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="L192" s="20" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="N192" s="20" t="n">
+        <v>5.036</v>
+      </c>
+      <c r="S192" s="20" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T192" s="20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="U192" s="20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="V192" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W192" s="20" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="X192" s="20" t="n">
+        <v>5.036</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="18" t="inlineStr">
+        <is>
+          <t>업무수탁료 수취</t>
+        </is>
+      </c>
+      <c r="S193" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U193" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
+        <is>
+          <t>보조금 수취</t>
+        </is>
+      </c>
+      <c r="D194" s="20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F194" s="20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W194" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>포상금 수취</t>
+        </is>
+      </c>
+      <c r="D195" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" s="20" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V195" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="D196" s="20" t="n">
+        <v>-0.877</v>
+      </c>
+      <c r="F196" s="20" t="n">
+        <v>-1.714</v>
+      </c>
+      <c r="H196" s="20" t="n">
+        <v>-0.799</v>
+      </c>
+      <c r="J196" s="20" t="n">
+        <v>-1.654</v>
+      </c>
+      <c r="L196" s="20" t="n">
+        <v>-0.676</v>
+      </c>
+      <c r="N196" s="20" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="S196" s="20" t="n">
+        <v>-0.5629999999999999</v>
+      </c>
+      <c r="T196" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" s="20" t="n">
+        <v>-1.714</v>
+      </c>
+      <c r="W196" s="20" t="n">
+        <v>-1.654</v>
+      </c>
+      <c r="X196" s="20" t="n">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="D197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="F197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H197" s="20" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="J197" s="20" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="L197" s="20" t="n">
+        <v>-21.342</v>
+      </c>
+      <c r="N197" s="20" t="n">
+        <v>-40.216</v>
+      </c>
+      <c r="S197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="T197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="U197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="V197" s="20" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="W197" s="20" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="X197" s="20" t="n">
+        <v>-40.216</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D198" s="12" t="n">
+        <v>-8.933</v>
+      </c>
+      <c r="F198" s="12" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="H198" s="12" t="n">
+        <v>133.474</v>
+      </c>
+      <c r="J198" s="12" t="n">
+        <v>290.705</v>
+      </c>
+      <c r="L198" s="12" t="n">
+        <v>112.367</v>
+      </c>
+      <c r="N198" s="12" t="n">
+        <v>413.183</v>
+      </c>
+      <c r="S198" s="12" t="n">
+        <v>-97.687</v>
+      </c>
+      <c r="T198" s="12" t="n">
+        <v>114.249</v>
+      </c>
+      <c r="U198" s="12" t="n">
+        <v>-66.91800000000001</v>
+      </c>
+      <c r="V198" s="12" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="W198" s="12" t="n">
+        <v>290.705</v>
+      </c>
+      <c r="X198" s="12" t="n">
+        <v>413.183</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="D199" s="20" t="n">
+        <v>-44.906</v>
+      </c>
+      <c r="F199" s="20" t="n">
+        <v>-47.532</v>
+      </c>
+      <c r="H199" s="20" t="n">
+        <v>-3.573</v>
+      </c>
+      <c r="J199" s="20" t="n">
+        <v>-18.939</v>
+      </c>
+      <c r="L199" s="20" t="n">
+        <v>-2.626</v>
+      </c>
+      <c r="N199" s="20" t="n">
+        <v>-4.413</v>
+      </c>
+      <c r="S199" s="20" t="n">
+        <v>-0.753</v>
+      </c>
+      <c r="T199" s="20" t="n">
+        <v>-18.462</v>
+      </c>
+      <c r="U199" s="20" t="n">
+        <v>-20.958</v>
+      </c>
+      <c r="V199" s="20" t="n">
+        <v>-47.532</v>
+      </c>
+      <c r="W199" s="20" t="n">
+        <v>-18.939</v>
+      </c>
+      <c r="X199" s="20" t="n">
+        <v>-4.413</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="F200" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" s="20" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U200" s="20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="V200" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>자산복구부채 이행 지출</t>
+        </is>
+      </c>
+      <c r="D201" s="20" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="F201" s="20" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="H201" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" s="20" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="W201" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>임차보증금 납입</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" s="20" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J202" s="20" t="n">
+        <v>-7.943</v>
+      </c>
+      <c r="L202" s="20" t="n">
+        <v>-119.172</v>
+      </c>
+      <c r="N202" s="20" t="n">
+        <v>-119.684</v>
+      </c>
+      <c r="S202" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" s="20" t="n">
+        <v>-11.25</v>
+      </c>
+      <c r="U202" s="20" t="n">
+        <v>-61.773</v>
+      </c>
+      <c r="V202" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W202" s="20" t="n">
+        <v>-7.943</v>
+      </c>
+      <c r="X202" s="20" t="n">
+        <v>-119.684</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>임차보증금 반환</t>
+        </is>
+      </c>
+      <c r="S203" s="20" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="T203" s="20" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="U203" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>임차보증금 회수</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="n">
+        <v>26.178</v>
+      </c>
+      <c r="F204" s="20" t="n">
+        <v>26.178</v>
+      </c>
+      <c r="H204" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U204" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V204" s="20" t="n">
+        <v>26.178</v>
+      </c>
+      <c r="W204" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F205" s="20" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J205" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T205" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U205" s="20" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="V205" s="20" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="W205" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D206" s="12" t="n">
+        <v>-26.257</v>
+      </c>
+      <c r="F206" s="12" t="n">
+        <v>-32.583</v>
+      </c>
+      <c r="H206" s="12" t="n">
+        <v>-4.293</v>
+      </c>
+      <c r="J206" s="12" t="n">
+        <v>-26.883</v>
+      </c>
+      <c r="L206" s="12" t="n">
+        <v>-121.799</v>
+      </c>
+      <c r="N206" s="12" t="n">
+        <v>-124.098</v>
+      </c>
+      <c r="S206" s="12" t="n">
+        <v>-0.6909999999999999</v>
+      </c>
+      <c r="T206" s="12" t="n">
+        <v>-34.654</v>
+      </c>
+      <c r="U206" s="12" t="n">
+        <v>-107.132</v>
+      </c>
+      <c r="V206" s="12" t="n">
+        <v>-32.583</v>
+      </c>
+      <c r="W206" s="12" t="n">
+        <v>-26.883</v>
+      </c>
+      <c r="X206" s="12" t="n">
+        <v>-124.098</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="18" t="inlineStr">
+        <is>
+          <t>단기차입</t>
+        </is>
+      </c>
+      <c r="F207" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N207" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W207" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="X207" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="18" t="inlineStr">
+        <is>
+          <t>단기차입금 상환</t>
+        </is>
+      </c>
+      <c r="F208" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="20" t="n">
+        <v>-50</v>
+      </c>
+      <c r="N208" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" s="20" t="n">
+        <v>-50</v>
+      </c>
+      <c r="X208" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="18" t="inlineStr">
+        <is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="D209" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="F209" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="H209" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="20" t="n">
+        <v>109</v>
+      </c>
+      <c r="W209" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="18" t="inlineStr">
+        <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="D210" s="20" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="F210" s="20" t="n">
+        <v>-19.976</v>
+      </c>
+      <c r="H210" s="20" t="n">
+        <v>-10.896</v>
+      </c>
+      <c r="J210" s="20" t="n">
+        <v>-21.792</v>
+      </c>
+      <c r="L210" s="20" t="n">
+        <v>-10.896</v>
+      </c>
+      <c r="N210" s="20" t="n">
+        <v>-21.792</v>
+      </c>
+      <c r="S210" s="20" t="n">
+        <v>-64.82899999999999</v>
+      </c>
+      <c r="T210" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" s="20" t="n">
+        <v>-19.976</v>
+      </c>
+      <c r="W210" s="20" t="n">
+        <v>-21.792</v>
+      </c>
+      <c r="X210" s="20" t="n">
+        <v>-21.792</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="18" t="inlineStr">
+        <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="D211" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" s="20" t="n">
+        <v>767.208</v>
+      </c>
+      <c r="J211" s="20" t="n">
+        <v>767.208</v>
+      </c>
+      <c r="L211" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" s="20" t="n">
+        <v>767.208</v>
+      </c>
+      <c r="X211" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="D212" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="20" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="J212" s="20" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="L212" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V212" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" s="20" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="X212" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 처분</t>
+        </is>
+      </c>
+      <c r="D213" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L213" s="20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N213" s="20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="S213" s="20" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="T213" s="20" t="n">
+        <v>323.787</v>
+      </c>
+      <c r="U213" s="20" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V213" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" s="20" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X213" s="20" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D214" s="12" t="n">
+        <v>99.92</v>
+      </c>
+      <c r="F214" s="12" t="n">
+        <v>89.024</v>
+      </c>
+      <c r="H214" s="12" t="n">
+        <v>756.3</v>
+      </c>
+      <c r="J214" s="12" t="n">
+        <v>753.104</v>
+      </c>
+      <c r="L214" s="12" t="n">
+        <v>-6.196</v>
+      </c>
+      <c r="N214" s="12" t="n">
+        <v>-17.092</v>
+      </c>
+      <c r="S214" s="12" t="n">
+        <v>-14.679</v>
+      </c>
+      <c r="T214" s="12" t="n">
+        <v>323.787</v>
+      </c>
+      <c r="U214" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V214" s="12" t="n">
+        <v>89.024</v>
+      </c>
+      <c r="W214" s="12" t="n">
+        <v>753.104</v>
+      </c>
+      <c r="X214" s="12" t="n">
+        <v>-17.092</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="18" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="D215" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="20" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="H215" s="20" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J215" s="20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L215" s="20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="N215" s="20" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="T215" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" s="20" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="W215" s="20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="X215" s="20" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="18" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="D190" s="20" t="n">
+      <c r="D216" s="20" t="n">
         <v>64.729</v>
       </c>
-      <c r="F190" s="20" t="n">
+      <c r="F216" s="20" t="n">
         <v>57.584</v>
       </c>
-      <c r="H190" s="20" t="n">
+      <c r="H216" s="20" t="n">
         <v>885.485</v>
       </c>
-      <c r="J190" s="20" t="n">
+      <c r="J216" s="20" t="n">
         <v>1016.928</v>
       </c>
-      <c r="L190" s="20" t="n">
+      <c r="L216" s="20" t="n">
         <v>-15.621</v>
       </c>
-      <c r="N190" s="20" t="n">
+      <c r="N216" s="20" t="n">
         <v>271.999</v>
       </c>
-      <c r="S190" s="20" t="n">
+      <c r="S216" s="20" t="n">
         <v>-113.057</v>
       </c>
-      <c r="T190" s="20" t="n">
+      <c r="T216" s="20" t="n">
         <v>403.381</v>
       </c>
-      <c r="U190" s="20" t="n">
+      <c r="U216" s="20" t="n">
         <v>-159.151</v>
       </c>
-      <c r="V190" s="20" t="n">
+      <c r="V216" s="20" t="n">
         <v>57.584</v>
       </c>
-      <c r="W190" s="20" t="n">
+      <c r="W216" s="20" t="n">
         <v>1016.928</v>
       </c>
-      <c r="X190" s="20" t="n">
+      <c r="X216" s="20" t="n">
         <v>271.999</v>
       </c>
     </row>
@@ -10745,7 +12268,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -12149,7 +13672,7 @@
       <c r="L42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -12201,7 +13724,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12253,7 +13776,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12305,7 +13828,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12357,7 +13880,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12409,7 +13932,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12461,7 +13984,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12471,43 +13994,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="45">
+      <c r="C49" s="46">
         <f>IFERROR(IF((IF(COUNT('연간'!G50:J50)&lt;4,"",SUM('연간'!G50:J50)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G50:J50)&lt;4,"",SUM('연간'!G50:J50)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!H50:K50)&lt;4,"",SUM('연간'!H50:K50)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H50:K50)&lt;4,"",SUM('연간'!H50:K50)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="46">
+      <c r="E49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!I50:L50)&lt;4,"",SUM('연간'!I50:L50)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I50:L50)&lt;4,"",SUM('연간'!I50:L50)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="46">
+      <c r="F49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!J50:M50)&lt;4,"",SUM('연간'!J50:M50)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J50:M50)&lt;4,"",SUM('연간'!J50:M50)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!K50:N50)&lt;4,"",SUM('연간'!K50:N50)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K50:N50)&lt;4,"",SUM('연간'!K50:N50)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="46">
         <f>IFERROR(IF(('연간'!T50)&lt;=0,"적자",H28/('연간'!T50)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="47">
         <f>IFERROR(IF(('연간'!U50)&lt;=0,"적자",I28/('연간'!U50)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="47">
         <f>IFERROR(IF(('연간'!V50)&lt;=0,"적자",J28/('연간'!V50)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="47">
         <f>IFERROR(IF(('연간'!W50)&lt;=0,"적자",K28/('연간'!W50)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="46">
+      <c r="L49" s="47">
         <f>IFERROR(IF(('연간'!X50)&lt;=0,"적자",L28/('연간'!X50)),"")</f>
         <v/>
       </c>
@@ -12531,7 +14054,7 @@
       <c r="L50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12583,7 +14106,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12635,7 +14158,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12687,7 +14210,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12739,7 +14262,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12791,7 +14314,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12861,7 +14384,7 @@
       <c r="L57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12913,7 +14436,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12923,49 +14446,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="49">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="49">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="49">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="48">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="49">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="48">
+      <c r="J59" s="49">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="48">
+      <c r="K59" s="49">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="48">
+      <c r="L59" s="49">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="A60" s="45" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12975,49 +14498,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>IFERROR(C9/(IF(COUNT('연간'!G17:J17)&lt;4,"",SUM('연간'!G17:J17)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="48">
+      <c r="D60" s="49">
         <f>IFERROR(D9/(IF(COUNT('연간'!H17:K17)&lt;4,"",SUM('연간'!H17:K17)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="49">
         <f>IFERROR(E9/(IF(COUNT('연간'!I17:L17)&lt;4,"",SUM('연간'!I17:L17)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48">
+      <c r="F60" s="49">
         <f>IFERROR(F9/(IF(COUNT('연간'!J17:M17)&lt;4,"",SUM('연간'!J17:M17)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="49">
         <f>IFERROR(G9/(IF(COUNT('연간'!K17:N17)&lt;4,"",SUM('연간'!K17:N17)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="47">
+      <c r="H60" s="48">
         <f>IFERROR(H9/('연간'!T17)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="49">
         <f>IFERROR(I9/('연간'!U17)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="48">
+      <c r="J60" s="49">
         <f>IFERROR(J9/('연간'!V17)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="48">
+      <c r="K60" s="49">
         <f>IFERROR(K9/('연간'!W17)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="48">
+      <c r="L60" s="49">
         <f>IFERROR(L9/('연간'!X17)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="45" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -13027,49 +14550,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <f>IFERROR(C19/(IF(COUNT('연간'!G17:J17)&lt;4,"",SUM('연간'!G17:J17)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="48">
+      <c r="D61" s="49">
         <f>IFERROR(D19/(IF(COUNT('연간'!H17:K17)&lt;4,"",SUM('연간'!H17:K17)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="49">
         <f>IFERROR(E19/(IF(COUNT('연간'!I17:L17)&lt;4,"",SUM('연간'!I17:L17)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="49">
         <f>IFERROR(F19/(IF(COUNT('연간'!J17:M17)&lt;4,"",SUM('연간'!J17:M17)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="49">
         <f>IFERROR(G19/(IF(COUNT('연간'!K17:N17)&lt;4,"",SUM('연간'!K17:N17)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="47">
+      <c r="H61" s="48">
         <f>IFERROR(H19/('연간'!T17)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="49">
         <f>IFERROR(I19/('연간'!U17)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="48">
+      <c r="J61" s="49">
         <f>IFERROR(J19/('연간'!V17)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="48">
+      <c r="K61" s="49">
         <f>IFERROR(K19/('연간'!W17)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="48">
+      <c r="L61" s="49">
         <f>IFERROR(L19/('연간'!X17)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -13079,43 +14602,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="49">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="49">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="49">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="48">
+      <c r="G62" s="49">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="47">
+      <c r="H62" s="48">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="49">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="48">
+      <c r="J62" s="49">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="48">
+      <c r="K62" s="49">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="48">
+      <c r="L62" s="49">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -13139,7 +14662,7 @@
       <c r="L63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -13191,7 +14714,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="A65" s="45" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13243,7 +14766,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="45" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13295,7 +14818,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="45" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -15291,24 +16814,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
